--- a/FILA DE TRABALHO/links_pendentes.xlsx
+++ b/FILA DE TRABALHO/links_pendentes.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,7 +11,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'links'!$A$1:$G$1272</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -77,19 +77,9 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -472,11 +462,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1440"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <dimension ref="A1:G1754"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="7.9296875" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -26160,8 +26150,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="F986" t="inlineStr"/>
-      <c r="G986" t="inlineStr"/>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
@@ -37908,13 +37896,7923 @@
         </is>
       </c>
     </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6063775,-46.9272795,3a,90y,113.64h,102.02t/data=!3m7!1e1!3m5!1s7kvNpB5VcyX9RAWJT7kGIw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-12.022846285101835%26panoid%3D7kvNpB5VcyX9RAWJT7kGIw%26yaw%3D113.64253928150804!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1441" t="n">
+        <v>2514</v>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>219386800</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>RUA AUGUSTO FLAVIO DA SILVA 183, 183, ESTANCIA</t>
+        </is>
+      </c>
+      <c r="E1441" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6064881,-46.9273043,3a,90y,79.8h,106.69t/data=!3m7!1e1!3m5!1sKwOlhG1tnUBbyXWvkZi5vA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-16.688546051672944%26panoid%3DKwOlhG1tnUBbyXWvkZi5vA%26yaw%3D79.80087525504709!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1442" t="n">
+        <v>2510</v>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>221807338</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>RUA AUGUSTO FLAVIO DA SILVA 183, 183, ESTANCIA</t>
+        </is>
+      </c>
+      <c r="E1442" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5954738,-46.9428513,3a,90y,12.65h,111.77t/data=!3m7!1e1!3m5!1s_dMWLG6V6pOSvd6hc5f-Tw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-21.77425320275111%26panoid%3D_dMWLG6V6pOSvd6hc5f-Tw%26yaw%3D12.65065221794173!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1443" t="n">
+        <v>1870</v>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>222494650</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>RUA SACRAMENTO 199, 199, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1443" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5954451,-46.9425453,3a,90y,24.47h,119.42t/data=!3m7!1e1!3m5!1sMAyRGHS2Aeu76z1GhIgysQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-29.41673858571123%26panoid%3DMAyRGHS2Aeu76z1GhIgysQ%26yaw%3D24.469471837079002!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>223390388</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>RUA SACRAMENTO 185, 185, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1444" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1444" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1444" t="inlineStr">
+        <is>
+          <t>confirmar - distancia (6.7m, 51 graus) e rumo (37.5m, 49 graus) nao concordam com confianca</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5954127,-46.9421452,3a,90y,350.05h,121.97t/data=!3m7!1e1!3m5!1sH_qReXvImWbV6XzZMgMjuA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-31.971684118936693%26panoid%3DH_qReXvImWbV6XzZMgMjuA%26yaw%3D350.0468166391902!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>223976980</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>RUA SACRAMENTO 147, 147, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5953961,-46.9418302,3a,90y,338.88h,110.5t/data=!3m7!1e1!3m5!1sMwVdLjadKcNC7c2pO_3GPA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-20.498377809208378%26panoid%3DMwVdLjadKcNC7c2pO_3GPA%26yaw%3D338.88148505195517!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>224318316</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>RUA SACRAMENTO 133, 133, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1446" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5953738,-46.9414941,3a,90y,330.07h,116.91t/data=!3m7!1e1!3m5!1sHqf0_uGbu6JU-x5T30PRhg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-26.914600177791215%26panoid%3DHqf0_uGbu6JU-x5T30PRhg%26yaw%3D330.0715686499237!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>220853359</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>PRACA DOUTOR HUGO LEVI 60, 60, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1447" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1447" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1447" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '184 R. Sacramento', cod_id escolhido e de 'PRACA DOUTOR HUGO LEVI 60, 60, CENTRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5953361,-46.941184,3a,90y,344.51h,111.4t/data=!3m7!1e1!3m5!1skdmDnao_vIjV75sjTdTJQw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-21.403687774142966%26panoid%3DkdmDnao_vIjV75sjTdTJQw%26yaw%3D344.5060391339377!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>219298347</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>PRACA DOUTOR HUGO LEVI 60, 60, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1448" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1448" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1448" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '218 R. Sacramento', cod_id escolhido e de 'PRACA DOUTOR HUGO LEVI 60, 60, CENTRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5953362,-46.9410097,3a,43y,45.99h,104.33t/data=!3m7!1e1!3m5!1sfGhaLxc00twui5agPTISAA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-14.333551277600819%26panoid%3DfGhaLxc00twui5agPTISAA%26yaw%3D45.989730574166074!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1449" t="n">
+        <v>2257</v>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>220853358</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 188, 188, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1449" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5952805,-46.9409182,3a,75y,41.77h,112.31t/data=!3m7!1e1!3m5!1sORx4xjZspJ9kq8meOpb3CQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.311950878852016%26panoid%3DORx4xjZspJ9kq8meOpb3CQ%26yaw%3D41.76979163419694!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1450" t="n">
+        <v>2259</v>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>224318258</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 188, 188, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1450" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5957312,-46.9415252,3a,90y,353.28h,106.84t/data=!3m7!1e1!3m5!1svsJTDrGZ-6wi9fDvnuUbSA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-16.841811140428632%26panoid%3DvsJTDrGZ-6wi9fDvnuUbSA%26yaw%3D353.28472169892484!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1451" t="n">
+        <v>2219</v>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>222494641</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>PRACA DOUTOR HUGO LEVI 66, 66, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1451" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5955564,-46.941453,3a,75y,208.44h,112.45t/data=!3m7!1e1!3m5!1sz-tDEJORgWdTsVVJzIkfxg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.451235293251486%26panoid%3Dz-tDEJORgWdTsVVJzIkfxg%26yaw%3D208.43668451060455!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1452" t="n">
+        <v>2215</v>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>223390387</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>PRACA DOUTOR HUGO LEVI 66, 66, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1452" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5958541,-46.9417214,3a,90y,281.04h,117.28t/data=!3m7!1e1!3m5!1svnpx-jbqtRloghc_rpCiEg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-27.275408179133336%26panoid%3Dvnpx-jbqtRloghc_rpCiEg%26yaw%3D281.0426634880612!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1453" t="n">
+        <v>2199</v>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>224318294</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1875, 1875, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1453" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5961668,-46.9419183,3a,90y,333.19h,110.23t/data=!3m7!1e1!3m5!1sCYluLdIsTnE38vnnC6YnTA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-20.227376185409412%26panoid%3DCYluLdIsTnE38vnnC6YnTA%26yaw%3D333.1925908625262!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>223976945</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1845, 1845, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1454" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.596342,-46.9419713,3a,90y,238.81h,115.98t/data=!3m7!1e1!3m5!1sRZdWMzJy6wz84toouJ-NIg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-25.98061199571984%26panoid%3DRZdWMzJy6wz84toouJ-NIg%26yaw%3D238.81231154431785!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1455" t="n">
+        <v>2225</v>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>220853339</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1815, 1815, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1455" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5964375,-46.9420083,3a,75y,315.75h,117.37t/data=!3m7!1e1!3m5!1sig2se9kCDjCJiAi2XFNFHA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-27.36877695574627%26panoid%3Dig2se9kCDjCJiAi2XFNFHA%26yaw%3D315.74722668332777!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1456" t="n">
+        <v>2224</v>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>219991742</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1815, 1815, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1456" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5966094,-46.941975,3a,90y,243.01h,127.78t/data=!3m7!1e1!3m5!1sZIyc3mfolfkPQzscecMz6w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-37.783005950589%26panoid%3DZIyc3mfolfkPQzscecMz6w%26yaw%3D243.01241188081008!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1457" t="n">
+        <v>2272</v>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>219298263</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1795, 1795, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1457" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5968096,-46.9419635,3a,48.9y,224.59h,115.49t/data=!3m7!1e1!3m5!1spdaq9ZG2ZCCdXwrbdtf7gA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-25.490655702284656%26panoid%3Dpdaq9ZG2ZCCdXwrbdtf7gA%26yaw%3D224.59394555927204!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1458" t="n">
+        <v>2314</v>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>219991681</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1765, 1765, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1458" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5970792,-46.9419524,3a,90y,246.17h,129.11t/data=!3m7!1e1!3m5!1scPMKBDfKmpPOIux3A-6IMQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-39.11159451547721%26panoid%3DcPMKBDfKmpPOIux3A-6IMQ%26yaw%3D246.1654285966436!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1459" t="n">
+        <v>2349</v>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>221621761</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1755, 1755, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1459" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5973564,-46.9419407,3a,75y,296.87h,114.98t/data=!3m7!1e1!3m5!1sZE70ndH0_htGqn3qiZJcrg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-24.98480448229496%26panoid%3DZE70ndH0_htGqn3qiZJcrg%26yaw%3D296.8735532791551!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1460" t="n">
+        <v>2388</v>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>220853338</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1731, 1731, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1460" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5975564,-46.9419334,3a,90y,283.01h,122.99t/data=!3m7!1e1!3m5!1smTZtxQuFYvsi6RLOxkgOvw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-32.99145030637881%26panoid%3DmTZtxQuFYvsi6RLOxkgOvw%26yaw%3D283.0060624099116!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1461" t="n">
+        <v>2432</v>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>221621758</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1715, 1715, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1461" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5976595,-46.9419386,3a,75y,223.9h,112.93t/data=!3m7!1e1!3m5!1sSvndijaBnxWM4GG7t2Apsg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.93227392978855%26panoid%3DSvndijaBnxWM4GG7t2Apsg%26yaw%3D223.8986325103992!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1462" t="n">
+        <v>2455</v>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>223390332</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1695, 1695, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1462" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5980166,-46.9418765,3a,35.9y,306.34h,103.47t/data=!3m7!1e1!3m5!1sPi1490SbfEZtjzBU9tqQxQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-13.474936902588851%26panoid%3DPi1490SbfEZtjzBU9tqQxQ%26yaw%3D306.3393156827838!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>219991693</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1530, 1530, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1463" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1463" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1463" t="inlineStr">
+        <is>
+          <t>confirmar - poste mais proximo (5.0m) tem 170 graus de diferenca de rumo, mas esta perto o suficiente pra ser so ruido de GPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5981139,-46.9418988,3a,41.2y,294.03h,100.6t/data=!3m7!1e1!3m5!1suS_OPDWEM1LTaJ1fxTEpeA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-10.604436900086114%26panoid%3DuS_OPDWEM1LTaJ1fxTEpeA%26yaw%3D294.02892702923185!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>219991677</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>RUA SAO CRISTOVAO 10, 10, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1464" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1464" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1464" t="inlineStr">
+        <is>
+          <t>cod_id escolhido pelo rumo, nao pela distancia (mais proximo a 11.0m tinha 104 graus de diferenca de rumo); ATENCAO nome de rua muito diferente: Street View diz o endereco e '349 Av. Pref. Aracely de Paula', cod_id escolhido e de 'RUA SAO CRISTOVAO 10, 10, CENTRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5980352,-46.9423551,3a,75y,226.71h,102.12t/data=!3m7!1e1!3m5!1sEKZOBtxPfPhmvpcYcU6kKA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-12.117205361974285%26panoid%3DEKZOBtxPfPhmvpcYcU6kKA%26yaw%3D226.70907811079647!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>452631419</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>RUA SAO CRISTOVAO 39, 39, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="E1465" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5980918,-46.9421813,3a,48.9y,144.97h,107.69t/data=!3m7!1e1!3m5!1sw_q3T_69bXBMr024kwVH1g!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-17.692477697253793%26panoid%3Dw_q3T_69bXBMr024kwVH1g%26yaw%3D144.97010340007796!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1466" t="n">
+        <v>2476</v>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>224318362</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>RUA SAO CRISTOVAO 15, 15, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="E1466" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5981139,-46.9420809,3a,41.2y,190.91h,105.53t/data=!3m7!1e1!3m5!1s31prdokW6XsWIA1GIuKVQQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-15.53069887749703%26panoid%3D31prdokW6XsWIA1GIuKVQQ%26yaw%3D190.91013567126114!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1467" t="n">
+        <v>2490</v>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>224318282</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>RUA SAO CRISTOVAO 15, 15, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="E1467" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.598462,-46.942098,3a,48.9y,294.68h,111.46t/data=!3m7!1e1!3m5!1sruZpoLXJzYeIkPvloshhSQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-21.458338973602736%26panoid%3DruZpoLXJzYeIkPvloshhSQ%26yaw%3D294.6836964537375!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>219991722</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1520, 1520, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1468" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1468" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1468" t="inlineStr">
+        <is>
+          <t>confirmar - poste mais proximo (8.4m) tem 162 graus de diferenca de rumo, mas esta perto o suficiente pra ser so ruido de GPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5986912,-46.9422175,3a,48.9y,304.69h,100.96t/data=!3m7!1e1!3m5!1sB4Q2QS8ocB9CCzxDodSGoA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-10.964568403133896%26panoid%3DB4Q2QS8ocB9CCzxDodSGoA%26yaw%3D304.68801031693437!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>219298324</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1615, 1615, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="E1469" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1469" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1469" t="inlineStr">
+        <is>
+          <t>confirmar - poste mais proximo (8.5m) tem 175 graus de diferenca de rumo, mas esta perto o suficiente pra ser so ruido de GPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5988588,-46.9422991,3a,32.8y,280.46h,99.48t/data=!3m7!1e1!3m5!1sh0qh8L77nK1vtf3Gmum6pw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-9.480960739953815%26panoid%3Dh0qh8L77nK1vtf3Gmum6pw%26yaw%3D280.4629864499314!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>224318357</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>RUA RIO BRANCO 1017, 1017, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="E1470" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1470" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1470" t="inlineStr">
+        <is>
+          <t>cod_id escolhido pelo rumo, nao pela distancia (mais proximo a 11.2m tinha 120 graus de diferenca de rumo); ATENCAO nome de rua muito diferente: Street View diz o endereco e '1615 Av. Pref. Aracely de Paula', cod_id escolhido e de 'RUA RIO BRANCO 1017, 1017, SAO CRISTOVAO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5993562,-46.9427036,3a,90y,328.45h,115.55t/data=!3m7!1e1!3m5!1sC4KIZsV_448vGdsLknDpMA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-25.550300710273476%26panoid%3DC4KIZsV_448vGdsLknDpMA%26yaw%3D328.4502335886438!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>221621836</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>RUA RIO BRANCO 1545, 1545, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="E1471" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1471" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1471" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '11 R. Cristóvão Viléla', cod_id escolhido e de 'RUA RIO BRANCO 1545, 1545, SAO CRISTOVAO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5994946,-46.9428295,3a,48.9y,210.43h,111.56t/data=!3m7!1e1!3m5!1sEKm3ziTdWOSxs76LxGAXQA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-21.557466509447536%26panoid%3DEKm3ziTdWOSxs76LxGAXQA%26yaw%3D210.42652577778694!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>219991781</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1535, 1535, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="E1472" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1472" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1472" t="inlineStr">
+        <is>
+          <t>confirmar - distancia (14.8m, 9 graus) e rumo (36.0m, 5 graus) nao concordam com confianca; ATENCAO nome de rua muito diferente: Street View diz o endereco e '11 R. Cristóvão Viléla', cod_id escolhido e de 'AVENIDA PREFEITO ARACELY DE PAULA 1535, 1535, SAO CRISTOVAO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5998702,-46.9428856,3a,75y,306.12h,105.22t/data=!3m7!1e1!3m5!1sYU_YWANvVYn2_Baad-7mLQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-15.21770447409223%26panoid%3DYU_YWANvVYn2_Baad-7mLQ%26yaw%3D306.12244790536135!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>224318376</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1515, 1515, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G1473" t="inlineStr">
+        <is>
+          <t>cod_id escolhido pelo rumo, nao pela distancia (mais proximo a 11.0m tinha 110 graus de diferenca de rumo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6000496,-46.9429703,3a,90y,302.6h,114.92t/data=!3m7!1e1!3m5!1s9oEFSM5cqRrc-4AmLIfhuw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-24.91742143160957%26panoid%3D9oEFSM5cqRrc-4AmLIfhuw%26yaw%3D302.5999194334424!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>220780195</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1505, 1505, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="E1474" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6002277,-46.9429731,3a,90y,257.11h,112.28t/data=!3m7!1e1!3m5!1sLHVUdbD-kXUJtm1QPrhrUw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.28097642863264%26panoid%3DLHVUdbD-kXUJtm1QPrhrUw%26yaw%3D257.11187257691466!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>221621863</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>RUA PAUL HARRIS 290, 290, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="E1475" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G1475" t="inlineStr">
+        <is>
+          <t>cod_id escolhido pelo rumo, nao pela distancia (mais proximo a 10.6m tinha 144 graus de diferenca de rumo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6004309,-46.9430027,3a,48.9y,219.09h,106.92t/data=!3m7!1e1!3m5!1sjyRg5q6LaWX5NqzBqnwouQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-16.92481290042204%26panoid%3DjyRg5q6LaWX5NqzBqnwouQ%26yaw%3D219.08706996629246!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1476" t="n">
+        <v>2402</v>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>222494686</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1455, 1455, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1476" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6004309,-46.9430027,3a,48.9y,249.15h,104.25t/data=!3m7!1e1!3m5!1sjyRg5q6LaWX5NqzBqnwouQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-14.249432436473853%26panoid%3DjyRg5q6LaWX5NqzBqnwouQ%26yaw%3D249.1505187463592!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1477" t="n">
+        <v>2379</v>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>220780194</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1455, 1455, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1477" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6007911,-46.9429516,3a,48.9y,268.9h,110.59t/data=!3m7!1e1!3m5!1sXyD3WA1thlV-kk_knhHLPg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-20.594715656217147%26panoid%3DXyD3WA1thlV-kk_knhHLPg%26yaw%3D268.89970088006373!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>223390432</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1425, 1425, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1478" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6010492,-46.9429766,3a,90y,298.3h,107.66t/data=!3m7!1e1!3m5!1sZoGDMJzbkxxfKaUZxJJN8A!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-17.663268304980022%26panoid%3DZoGDMJzbkxxfKaUZxJJN8A%26yaw%3D298.29835127684316!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>219298399</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1385, 1385, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1479" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1479" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1479" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '470 R. Zéca do Alfredo', cod_id escolhido e de 'AVENIDA PREFEITO ARACELY DE PAULA 1385, 1385, JOAO RIBEIRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6012415,-46.9430077,3a,90y,270.38h,126.25t/data=!3m7!1e1!3m5!1s45rVAxIoUIbOLajX_aT21A!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-36.25188369751562%26panoid%3D45rVAxIoUIbOLajX_aT21A%26yaw%3D270.38211733830735!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>219991799</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1375, 1375, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1480" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1480" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1480" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '470 R. Zéca do Alfredo', cod_id escolhido e de 'AVENIDA PREFEITO ARACELY DE PAULA 1375, 1375, JOAO RIBEIRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6003272,-46.9429805,3a,73.9y,43.39h,104.38t/data=!3m7!1e1!3m5!1sf7BeoPqokrJKam1Nz1fYzQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-14.381231234004659%26panoid%3Df7BeoPqokrJKam1Nz1fYzQ%26yaw%3D43.39120253824248!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1481" t="n">
+        <v>2452</v>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>222494656</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1290, 1290, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1481" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6000496,-46.9429703,3a,48.9y,78.88h,108.14t/data=!3m7!1e1!3m5!1s9oEFSM5cqRrc-4AmLIfhuw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-18.14269657053555%26panoid%3D9oEFSM5cqRrc-4AmLIfhuw%26yaw%3D78.87701590782561!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1482" t="n">
+        <v>2450</v>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>223390313</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1310, 1310, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1482" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5997819,-46.9428482,3a,75y,120.45h,114.72t/data=!3m7!1e1!3m5!1swP-cjvNnpgXjUFlTxSAPQQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-24.717304745888313%26panoid%3DwP-cjvNnpgXjUFlTxSAPQQ%26yaw%3D120.45051852321879!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1483" t="n">
+        <v>2451</v>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>223976972</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1330, 1330, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1483" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5995247,-46.9427049,3a,73.9y,146.59h,115.31t/data=!3m7!1e1!3m5!1s78Gn5axaUwdZ0Z5oFhFEww!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-25.311344242711797%26panoid%3D78Gn5axaUwdZ0Z5oFhFEww%26yaw%3D146.58799029802393!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1484" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>224318300</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 127, 127, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5994473,-46.9426525,3a,39.4y,67.78h,101.75t/data=!3m7!1e1!3m5!1sVozJyc0Ex3wYt3AAcLu8GA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-11.746144972182151%26panoid%3DVozJyc0Ex3wYt3AAcLu8GA%26yaw%3D67.78309083632186!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1485" t="n">
+        <v>2512</v>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>219298323</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>RUA RIO BRANCO 1545, 1545, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5992145,-46.94247,3a,75y,60.31h,116.26t/data=!3m7!1e1!3m5!1sY7nJS-JV2o2kATDeLcEglw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-26.256281322239204%26panoid%3DY7nJS-JV2o2kATDeLcEglw%26yaw%3D60.313241965003904!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1486" t="n">
+        <v>2522</v>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>219991721</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>RUA RIO BRANCO 1545, 1545, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5986096,-46.9421769,3a,75y,162.06h,118.39t/data=!3m7!1e1!3m5!1sDpGZcIQO-H0L2aNLa_RsYw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-28.394734518642963%26panoid%3DDpGZcIQO-H0L2aNLa_RsYw%26yaw%3D162.05997220877074!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1487" t="n">
+        <v>2531</v>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>224318299</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>RUA RIO BRANCO 1017, 1017, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="E1487" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.598462,-46.942098,3a,75y,112.17h,116.46t/data=!3m7!1e1!3m5!1sruZpoLXJzYeIkPvloshhSQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-26.46285407768019%26panoid%3DruZpoLXJzYeIkPvloshhSQ%26yaw%3D112.17227528012127!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1488" t="n">
+        <v>2445</v>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>224292683</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>AVENIDA DIVINO ALVES FERREIRA 493, 493, ESTANCIA</t>
+        </is>
+      </c>
+      <c r="E1488" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5982846,-46.9419945,3a,75y,88.32h,108.2t/data=!3m7!1e1!3m5!1sz3uoC6aWEsXK_fC_BMJXEQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-18.197862758104662%26panoid%3Dz3uoC6aWEsXK_fC_BMJXEQ%26yaw%3D88.3229150834838!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1489" t="n">
+        <v>2551</v>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>224318270</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1514, 1514, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1489" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5986096,-46.9421769,3a,46.9y,158.5h,109.11t/data=!3m7!1e1!3m5!1sDpGZcIQO-H0L2aNLa_RsYw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-19.109686132592287%26panoid%3DDpGZcIQO-H0L2aNLa_RsYw%26yaw%3D158.49849176112087!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1490" t="n">
+        <v>2541</v>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>219298324</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1615, 1615, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="E1490" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1490" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1490" t="inlineStr">
+        <is>
+          <t>COLISAO DE COD_ID - movido pra pasta DUPLICADOS, ver duplicados_para_validar.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5982306,-46.9416852,3a,48.9y,147.12h,105.39t/data=!3m7!1e1!3m5!1s9TcRcJ4j--oezx__Nhz_0A!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-15.393380563635901%26panoid%3D9TcRcJ4j--oezx__Nhz_0A%26yaw%3D147.1241700386666!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>219298279</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>RUA PADRE ALAOR 55, 55, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1491" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5981139,-46.9418988,3a,41.2y,45.34h,110.48t/data=!3m7!1e1!3m5!1suS_OPDWEM1LTaJ1fxTEpeA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-20.48031833548788%26panoid%3DuS_OPDWEM1LTaJ1fxTEpeA%26yaw%3D45.33803043467011!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>219991693</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1530, 1530, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1492" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1492" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1492" t="inlineStr">
+        <is>
+          <t>COLISAO DE COD_ID - movido pra pasta DUPLICADOS, ver duplicados_para_validar.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5977301,-46.9418117,3a,63.6y,156.61h,118.73t/data=!3m7!1e1!3m5!1ss418CFqhyy5yWpUvQuhhhw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-28.73398617152249%26panoid%3Ds418CFqhyy5yWpUvQuhhhw%26yaw%3D156.61195741963206!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>220780275</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1550, 1550, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1493" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5975483,-46.9418027,3a,90y,93.44h,127.52t/data=!3m7!1e1!3m5!1srE5o1vKp63csd-9sdUKwtA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-37.51571524003353%26panoid%3DrE5o1vKp63csd-9sdUKwtA%26yaw%3D93.43642896738889!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>223976912</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>RUA HEITOR MONTANDON 113, 113, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1494" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1494" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1494" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '273 Av. Pref. Aracely de Paula', cod_id escolhido e de 'RUA HEITOR MONTANDON 113, 113, CENTRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5973763,-46.941701,3a,90y,304.21h,119.64t/data=!3m7!1e1!3m5!1sF3P_v3uWCx6ul0jYScFq0w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-29.638602416892198%26panoid%3DF3P_v3uWCx6ul0jYScFq0w%26yaw%3D304.2117841424082!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1495" t="n">
+        <v>2480</v>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>224318273</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>RUA HEITOR MONTANDON 113, 113, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1495" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5969832,-46.9418253,3a,43y,156.82h,107.74t/data=!3m7!1e1!3m5!1sx-xZIS9TytNOEHVftPTBzg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-17.740939179850244%26panoid%3Dx-xZIS9TytNOEHVftPTBzg%26yaw%3D156.8157985683484!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1496" t="n">
+        <v>2424</v>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>219991686</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1620, 1620, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1496" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5969832,-46.9418253,3a,43y,18.59h,113.57t/data=!3m7!1e1!3m5!1sx-xZIS9TytNOEHVftPTBzg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-23.56959921066526%26panoid%3Dx-xZIS9TytNOEHVftPTBzg%26yaw%3D18.591754642003494!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1497" t="n">
+        <v>2373</v>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>219298284</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1640, 1640, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1497" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6002731,-46.9458261,3a,90y,295.46h,113.5t/data=!3m7!1e1!3m5!1sfF5cXNvBzEDgZZwrfU19xQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-23.50115744274902%26panoid%3DfF5cXNvBzEDgZZwrfU19xQ%26yaw%3D295.46225710309926!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1498" t="n">
+        <v>1607</v>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>222494557</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>RUA MARCELINA CARDOSO 280, 280, SANTA LUZIA</t>
+        </is>
+      </c>
+      <c r="E1498" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5995475,-46.944496,3a,54.7y,173.25h,108.94t/data=!3m7!1e1!3m5!1s3ppXlidRcBEnamW7bHzLTQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-18.94256743682908%26panoid%3D3ppXlidRcBEnamW7bHzLTQ%26yaw%3D173.24578746674945!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>219991932</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>RUA CAMPOS ALTOS 103, 103, SANTA LUZIA</t>
+        </is>
+      </c>
+      <c r="E1499" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.599881,-46.9442493,3a,90y,231.12h,119.91t/data=!3m7!1e1!3m5!1sIw_e2iKtXoeV4W1eclTP0Q!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-29.908417047928324%26panoid%3DIw_e2iKtXoeV4W1eclTP0Q%26yaw%3D231.12257044238288!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>222494488</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>RUA CAMPOS ALTOS 67, 67, SANTA LUZIA</t>
+        </is>
+      </c>
+      <c r="E1500" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6001603,-46.9440334,3a,90y,217.39h,112.26t/data=!3m7!1e1!3m5!1sO3cMmiADjdE9X9_FqvdGWQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.260429651637054%26panoid%3DO3cMmiADjdE9X9_FqvdGWQ%26yaw%3D217.39345053264546!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>219991931</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>RUA CAMPOS ALTOS 41, 41, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="E1501" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.60033,-46.9439065,3a,48.9y,185.66h,105.67t/data=!3m7!1e1!3m5!1s3gVGrdlun8v-yONXFLrdyg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-15.672507622087394%26panoid%3D3gVGrdlun8v-yONXFLrdyg%26yaw%3D185.66138464693964!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1502" t="n">
+        <v>2138</v>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>223976732</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>RUA CAMPOS ALTOS 21, 21, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="E1502" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.600533,-46.9438889,3a,90y,99.28h,119.66t/data=!3m7!1e1!3m5!1sEDMI3FuxSABIcTNIyn24yQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-29.66251786160541%26panoid%3DEDMI3FuxSABIcTNIyn24yQ%26yaw%3D99.27650929811617!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1503" t="n">
+        <v>2162</v>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>219991793</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>RUA PAUL HARRIS 397, 397, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1503" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6004832,-46.9438545,3a,90y,129.93h,112.59t/data=!3m7!1e1!3m5!1sEziyFtJmV38y5-XF-_JBzA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.58761688489001%26panoid%3DEziyFtJmV38y5-XF-_JBzA%26yaw%3D129.92577349693084!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1504" t="n">
+        <v>2180</v>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>224318067</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>RUA PAUL HARRIS 363, 363, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1504" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6001693,-46.9437525,3a,77.2y,213.59h,120.65t/data=!3m7!1e1!3m5!1snc3J8MA-xwEG-t_KIZJohg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-30.648509274445615%26panoid%3Dnc3J8MA-xwEG-t_KIZJohg%26yaw%3D213.58920650938884!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>219298400</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>RUA CAMPOS ALTOS 22, 22, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="E1505" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1505" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1505" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '99 R. Patrocínio', cod_id escolhido e de 'RUA CAMPOS ALTOS 22, 22, SAO CRISTOVAO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6000033,-46.9436937,3a,75y,352.49h,112.85t/data=!3m7!1e1!3m5!1slzB7g3TBye6tkfL9QS4dvA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.845475983523727%26panoid%3DlzB7g3TBye6tkfL9QS4dvA%26yaw%3D352.4886507503888!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>1501916767</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>RUA PATROCINIO 84, 84, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="E1506" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5996311,-46.9435626,3a,90y,284.23h,126.77t/data=!3m7!1e1!3m5!1ssVzfRU8LzbTdKrwDyps3AQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-36.765617600330515%26panoid%3DsVzfRU8LzbTdKrwDyps3AQ%26yaw%3D284.2302131332273!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>219298390</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>RUA PATROCINIO 42, 42, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="E1507" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6004571,-46.9434587,3a,90y,178.63h,124.68t/data=!3m7!1e1!3m5!1sQTGANNkSz-31gP_fCf6umw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-34.68148658655414%26panoid%3DQTGANNkSz-31gP_fCf6umw%26yaw%3D178.62919530636879!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>221621850</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>RUA PAUL HARRIS 347, 347, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1508" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6008861,-46.9438816,3a,90y,82.69h,119.06t/data=!3m7!1e1!3m5!1ssDLmZqNA30A5ooX1gh0OZA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-29.060865087836234%26panoid%3DsDLmZqNA30A5ooX1gh0OZA%26yaw%3D82.68857285874853!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>222494683</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>RUA JOAO MAGALHAES 33, 33, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1509" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1509" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1509" t="inlineStr">
+        <is>
+          <t>confirmar - distancia (0.9m, 65 graus) e rumo (60.4m, 40 graus) nao concordam com confianca</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6012562,-46.943869,3a,90y,94.55h,121.17t/data=!3m7!1e1!3m5!1sZNSxnm28Lxab6XDP3ypBSA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-31.1662751083431%26panoid%3DZNSxnm28Lxab6XDP3ypBSA%26yaw%3D94.54862827377612!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>223977048</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>RUA JOAO MAGALHAES 77, 77, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1510" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6015915,-46.9438499,3a,90y,116.72h,114.52t/data=!3m7!1e1!3m5!1sm_9_HTAg_2hbGZl8t4CpQQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-24.518946131880682%26panoid%3Dm_9_HTAg_2hbGZl8t4CpQQ%26yaw%3D116.72467245361625!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1511" t="n">
+        <v>2193</v>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>223390431</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>RUA JOAO BATISTA FERNANDES 400, 400, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1511" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6016662,-46.943815,3a,48.9y,51.58h,118.14t/data=!3m7!1e1!3m5!1swcSLeOo-t03_oMmDkoin4Q!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-28.142781408065346%26panoid%3DwcSLeOo-t03_oMmDkoin4Q%26yaw%3D51.578258884016435!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1512" t="n">
+        <v>2211</v>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>219991792</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>RUA JOAO MAGALHAES 103, 103, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1512" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6020409,-46.9438299,3a,48.9y,24.97h,111.95t/data=!3m7!1e1!3m5!1sPzUGIhHS54oqfQviguauTA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-21.948685384903797%26panoid%3DPzUGIhHS54oqfQviguauTA%26yaw%3D24.970279946775108!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>224318377</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>RUA JOAO MAGALHAES 164, 164, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1513" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1513" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1513" t="inlineStr">
+        <is>
+          <t>confirmar - distancia (15.9m, 34 graus) e rumo (44.9m, 21 graus) nao concordam com confianca</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6022323,-46.9438292,3a,90y,97.22h,120.81t/data=!3m7!1e1!3m5!1s5hprhny6ZNmKGo3CoXQmWg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-30.808186557884156%26panoid%3D5hprhny6ZNmKGo3CoXQmWg%26yaw%3D97.2240229118285!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>224318385</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>RUA JOAO MAGALHAES 178, 178, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1514" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1514" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1514" t="inlineStr">
+        <is>
+          <t>confirmar - distancia (3.4m, 131 graus) e rumo (49.4m, 72 graus) nao concordam com confianca</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6024081,-46.9438298,3a,48.9y,144.73h,112.34t/data=!3m7!1e1!3m5!1swiiISxkj2wlSFEpXB7idMA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.342988951404024%26panoid%3DwiiISxkj2wlSFEpXB7idMA%26yaw%3D144.7264408466252!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>219298220</t>
+        </is>
+      </c>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>RUA JOAO MAGALHAES 210, 210, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1515" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5932672,-46.9407807,3a,75y,358.67h,112.41t/data=!3m7!1e1!3m5!1sRL_GRiL8qu7L-r6ymgR5iQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.409464790639845%26panoid%3DRL_GRiL8qu7L-r6ymgR5iQ%26yaw%3D358.67096085282805!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1516" t="n">
+        <v>1857</v>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>222494583</t>
+        </is>
+      </c>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 0, 0, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1516" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5934283,-46.9405805,3a,90y,67.16h,117.6t/data=!3m7!1e1!3m5!1stO5-Gkp3Q1vIPVSuRepG0A!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-27.595652638689018%26panoid%3DtO5-Gkp3Q1vIPVSuRepG0A%26yaw%3D67.15651109275205!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1517" t="n">
+        <v>1938</v>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>222494581</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 0, 0, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1517" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5937011,-46.9402643,3a,90y,29.03h,118.7t/data=!3m7!1e1!3m5!1sugMTYHzKUozWjVcul95NVw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-28.702670152361947%26panoid%3DugMTYHzKUozWjVcul95NVw%26yaw%3D29.030921942284145!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1518" t="n">
+        <v>2038</v>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>223390351</t>
+        </is>
+      </c>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 62, 62, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1518" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5939342,-46.9399927,3a,90y,35.73h,118.71t/data=!3m7!1e1!3m5!1suVb27e6EJFMC46BnNvgiyA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-28.711666367693724%26panoid%3DuVb27e6EJFMC46BnNvgiyA%26yaw%3D35.72929237007089!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1519" t="n">
+        <v>2132</v>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>223976910</t>
+        </is>
+      </c>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 137, 137, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1519" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5938167,-46.9401297,3a,63.6y,210.86h,113.63t/data=!3m7!1e1!3m5!1s2JEArOOSOQeOscMv9cTcpA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-23.634346909476236%26panoid%3D2JEArOOSOQeOscMv9cTcpA%26yaw%3D210.86298278579372!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1520" t="n">
+        <v>2092</v>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>221621727</t>
+        </is>
+      </c>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 70, 70, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1520" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5940533,-46.9399161,3a,90y,163.65h,113.74t/data=!3m7!1e1!3m5!1smWpgreXoybTmUiz7H-Vm8w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-23.74003697118785%26panoid%3DmWpgreXoybTmUiz7H-Vm8w%26yaw%3D163.65230045796778!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1521" t="n">
+        <v>2194</v>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>219298227</t>
+        </is>
+      </c>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 120, 120, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1521" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5944774,-46.9394075,3a,90y,240.55h,115.82t/data=!3m7!1e1!3m5!1sM4jOCYt_NuBDyoIn6byhsw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-25.824173638334173%26panoid%3DM4jOCYt_NuBDyoIn6byhsw%26yaw%3D240.55153385182828!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1522" t="n">
+        <v>2357</v>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>219654503</t>
+        </is>
+      </c>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 166, 166, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1522" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5946031,-46.9392497,3a,90y,221.72h,127.36t/data=!3m7!1e1!3m5!1shQ33psWv_00BU70ZvyvT7w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-37.3601619690326%26panoid%3DhQ33psWv_00BU70ZvyvT7w%26yaw%3D221.72089706321492!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1523" t="n">
+        <v>2442</v>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>223455608</t>
+        </is>
+      </c>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 170, 170, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1523" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5947862,-46.9389625,3a,75y,209.45h,124.38t/data=!3m7!1e1!3m5!1s1eOK913czVtpnUmGakYjvw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-34.377066383649876%26panoid%3D1eOK913czVtpnUmGakYjvw%26yaw%3D209.44608297831368!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1524" t="n">
+        <v>2539</v>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>222494805</t>
+        </is>
+      </c>
+      <c r="D1524" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 250, 250, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1524" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.59504,-46.9387314,3a,90y,195.28h,125.08t/data=!3m7!1e1!3m5!1sysyoEalH6khj69L-csPAHw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-35.084845390448166%26panoid%3DysyoEalH6khj69L-csPAHw%26yaw%3D195.27640078501315!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1525" t="n">
+        <v>2637</v>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>223977765</t>
+        </is>
+      </c>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 274, 274, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1525" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5952259,-46.9385152,3a,44.9y,148.87h,110.02t/data=!3m7!1e1!3m5!1sGywlMCdsw-WE7WLrm1S1Tg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-20.019961199640676%26panoid%3DGywlMCdsw-WE7WLrm1S1Tg%26yaw%3D148.87324514487366!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1526" t="n">
+        <v>2713</v>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>219992863</t>
+        </is>
+      </c>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 320, 320, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1526" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5951583,-46.9385105,3a,90y,8.53h,115.64t/data=!3m7!1e1!3m5!1sHwNgkSu9iDH523l7bStLuQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-25.63657061120192%26panoid%3DHwNgkSu9iDH523l7bStLuQ%26yaw%3D8.529876801930769!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1527" t="n">
+        <v>2675</v>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>224357744</t>
+        </is>
+      </c>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 301, 301, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1527" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5949776,-46.938734,3a,48.9y,338.9h,111.2t/data=!3m7!1e1!3m5!1sBjHaiz_aZcmbz5VHE0G_FA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-21.197512651992113%26panoid%3DBjHaiz_aZcmbz5VHE0G_FA%26yaw%3D338.90145363769534!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1528" t="n">
+        <v>2588</v>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>223455560</t>
+        </is>
+      </c>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 281, 281, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1528" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5946629,-46.9391076,3a,90y,80.54h,112.65t/data=!3m7!1e1!3m5!1sHRWxFbr--ROMWQfQesTLCg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.653091288553853%26panoid%3DHRWxFbr--ROMWQfQesTLCg%26yaw%3D80.53934283831416!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1529" t="n">
+        <v>2475</v>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>221704164</t>
+        </is>
+      </c>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 231, 231, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1529" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5952031,-46.9382586,3a,90y,340.13h,117.06t/data=!3m7!1e1!3m5!1sC644hIvwQuB0mqx_SEEB6Q!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-27.05777780109254%26panoid%3DC644hIvwQuB0mqx_SEEB6Q%26yaw%3D340.1263853714046!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1530" t="n">
+        <v>2708</v>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>223977767</t>
+        </is>
+      </c>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>RUA ALMEIDA CAMPOS 364, 364, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1530" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5949935,-46.9380454,3a,90y,320.59h,121.32t/data=!3m7!1e1!3m5!1s8OdaWPyajORiKFQiB0OoOA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-31.31845715634489%26panoid%3D8OdaWPyajORiKFQiB0OoOA%26yaw%3D320.5914094470712!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>222494810</t>
+        </is>
+      </c>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>RUA ALMEIDA CAMPOS 330, 330, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1531" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5947963,-46.9378302,3a,90y,307.9h,110.82t/data=!3m7!1e1!3m5!1sKDsdiFLV7ewzaqSk0zMH3g!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-20.818296272349613%26panoid%3DKDsdiFLV7ewzaqSk0zMH3g%26yaw%3D307.89715186197435!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>223455564</t>
+        </is>
+      </c>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>RUA ALMEIDA CAMPOS 306, 306, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1532" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.59536,-46.9397019,3a,75y,347.54h,113.83t/data=!3m7!1e1!3m5!1s5RVb8a1tmuGZj6BElnERQA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-23.834929177587256%26panoid%3D5RVb8a1tmuGZj6BElnERQA%26yaw%3D347.5371082612378!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>223455631</t>
+        </is>
+      </c>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>RUA DOM BOSCO 153, 153, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1533" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1533" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1533" t="inlineStr">
+        <is>
+          <t>confirmar - poste mais proximo (8.6m) tem 130 graus de diferenca de rumo, mas esta perto o suficiente pra ser so ruido de GPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5954696,-46.9395495,3a,75y,329.7h,116.82t/data=!3m7!1e1!3m5!1sDN-cQqsRE8vbMO7W7H0IYg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-26.819060972950837%26panoid%3DDN-cQqsRE8vbMO7W7H0IYg%26yaw%3D329.7040524850523!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>223455631</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>RUA DOM BOSCO 153, 153, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1534" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1534" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1534" t="inlineStr">
+        <is>
+          <t>COLISAO DE COD_ID - movido pra pasta DUPLICADOS, ver duplicados_para_validar.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5955152,-46.9394658,3a,75y,76.07h,108.15t/data=!3m7!1e1!3m5!1siE6_uuT8G9Sei6EZCD_Tyw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-18.150200639247473%26panoid%3DiE6_uuT8G9Sei6EZCD_Tyw%26yaw%3D76.07086021833832!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>223977841</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>RUA DOM BOSCO 183, 183, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1535" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1535" t="inlineStr"/>
+      <c r="G1535" t="inlineStr"/>
+    </row>
+    <row r="1536">
+      <c r="A1536" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5956939,-46.9391107,3a,75y,333.72h,113.2t/data=!3m7!1e1!3m5!1sci3RMmm-WNc9kivoPD-00w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-23.19721305394131%26panoid%3Dci3RMmm-WNc9kivoPD-00w%26yaw%3D333.71839328565966!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>224357812</t>
+        </is>
+      </c>
+      <c r="D1536" t="inlineStr">
+        <is>
+          <t>RUA DOM BOSCO 183, 183, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1536" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5957866,-46.9389185,3a,90y,44.54h,120.37t/data=!3m7!1e1!3m5!1sOOVKLWp_RL2AGgiTLqWrEg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-30.36690123954996%26panoid%3DOOVKLWp_RL2AGgiTLqWrEg%26yaw%3D44.537276940315266!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1537" t="n">
+        <v>2745</v>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>219992957</t>
+        </is>
+      </c>
+      <c r="D1537" t="inlineStr">
+        <is>
+          <t>RUA DOM BOSCO 229, 229, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1537" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5958092,-46.9388398,3a,90y,329.68h,116.9t/data=!3m7!1e1!3m5!1sgNXKeNoI7u53CjiXYIuU8A!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-26.90170506124859%26panoid%3DgNXKeNoI7u53CjiXYIuU8A%26yaw%3D329.679623494411!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1538" t="n">
+        <v>2754</v>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>220854148</t>
+        </is>
+      </c>
+      <c r="D1538" t="inlineStr">
+        <is>
+          <t>RUA DOM BOSCO 229, 229, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1538" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5956014,-46.9386391,3a,90y,344.61h,121.37t/data=!3m7!1e1!3m5!1skxmgc9BB6w9iOhg6r0EOxw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-31.365737819380556%26panoid%3Dkxmgc9BB6w9iOhg6r0EOxw%26yaw%3D344.6054797142836!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>1003482071</t>
+        </is>
+      </c>
+      <c r="D1539" t="inlineStr">
+        <is>
+          <t>RUA ALMEIDA CAMPOS 424, 424, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1539" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.595461,-46.9384996,3a,48.9y,14.17h,111.9t/data=!3m7!1e1!3m5!1sBJYLEVVW-2VnD0FyAZi_8A!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-21.898102624817184%26panoid%3DBJYLEVVW-2VnD0FyAZi_8A%26yaw%3D14.173129764684456!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1540" t="n">
+        <v>2731</v>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>219384928</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 320, 320, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1540" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5955863,-46.9402347,3a,75y,73.98h,114.29t/data=!3m7!1e1!3m5!1s64Y6MqcoA9HT94ac6JnBcQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-24.29109050205065%26panoid%3D64Y6MqcoA9HT94ac6JnBcQ%26yaw%3D73.98021492235293!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>220247663</t>
+        </is>
+      </c>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>RUA FRANCELINO CARDOSO 36, 36, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1541" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5954055,-46.938206,3a,63.6y,339.12h,121.75t/data=!3m7!1e1!3m5!1sNkFr9TFhj2atYlW2au7LXw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-31.754672620432785%26panoid%3DNkFr9TFhj2atYlW2au7LXw%26yaw%3D339.12139436157906!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1542" t="n">
+        <v>2752</v>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>224357745</t>
+        </is>
+      </c>
+      <c r="D1542" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 321, 321, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1542" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.595468,-46.9381294,3a,90y,80.8h,119.03t/data=!3m7!1e1!3m5!1sg_UteYgc7HqhFoiCS_BVRg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-29.025653596198097%26panoid%3Dg_UteYgc7HqhFoiCS_BVRg%26yaw%3D80.79823851373743!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1543" t="n">
+        <v>2792</v>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>220854101</t>
+        </is>
+      </c>
+      <c r="D1543" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 353, 353, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1543" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5956468,-46.9379232,3a,90y,12.68h,132.14t/data=!3m7!1e1!3m5!1sIGZ5y5-Ty-3hyryyHaem4g!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-42.13599908460509%26panoid%3DIGZ5y5-Ty-3hyryyHaem4g%26yaw%3D12.677816906648552!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1544" t="n">
+        <v>2842</v>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>223977766</t>
+        </is>
+      </c>
+      <c r="D1544" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 365, 365, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1544" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.595833,-46.937715,3a,90y,30.1h,119.73t/data=!3m7!1e1!3m5!1sRaUJiqBWikBnzh8oZKg5nw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-29.731618405703813%26panoid%3DRaUJiqBWikBnzh8oZKg5nw%26yaw%3D30.0975809474699!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1545" t="n">
+        <v>2900</v>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>219384924</t>
+        </is>
+      </c>
+      <c r="D1545" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 385, 385, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1545" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5960725,-46.9374276,3a,90y,31.61h,115.1t/data=!3m7!1e1!3m5!1szvMUcWtKCqxXE4QexI0L2g!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-25.098303258468178%26panoid%3DzvMUcWtKCqxXE4QexI0L2g%26yaw%3D31.60628689440413!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1546" t="n">
+        <v>2970</v>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>222494737</t>
+        </is>
+      </c>
+      <c r="D1546" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 381, 381, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1546" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.596321,-46.9371358,3a,90y,43.01h,119.08t/data=!3m7!1e1!3m5!1swpOWX1-KPWToNKQc7NxlHA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-29.081674472699504%26panoid%3DwpOWX1-KPWToNKQc7NxlHA%26yaw%3D43.00862846990125!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1547" t="n">
+        <v>3057</v>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>219992893</t>
+        </is>
+      </c>
+      <c r="D1547" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 407, 407, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1547" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.596567,-46.9368347,3a,90y,27.84h,119.45t/data=!3m7!1e1!3m5!1scqgbQds2sHYwL2EDLIsk5w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-29.445959277341288%26panoid%3DcqgbQds2sHYwL2EDLIsk5w%26yaw%3D27.842962529847348!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1548" t="n">
+        <v>3134</v>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>221704135</t>
+        </is>
+      </c>
+      <c r="D1548" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 427, 427, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1548" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5968093,-46.9365428,3a,90y,27.31h,115.54t/data=!3m7!1e1!3m5!1stBi8vdF_uld8s0gojHXtYQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-25.54065279915325%26panoid%3DtBi8vdF_uld8s0gojHXtYQ%26yaw%3D27.306069982984347!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1549" t="n">
+        <v>3210</v>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>221704137</t>
+        </is>
+      </c>
+      <c r="D1549" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 513, 513, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1549" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5969629,-46.9364685,3a,90y,175.53h,135.18t/data=!3m7!1e1!3m5!1slP1DquFlhpZuX_ulrq3NwA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-45.179198398085475%26panoid%3DlP1DquFlhpZuX_ulrq3NwA%26yaw%3D175.53265674569178!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1550" t="n">
+        <v>3258</v>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>221704405</t>
+        </is>
+      </c>
+      <c r="D1550" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 0, 0, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1550" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.596712,-46.9367575,3a,90y,169.43h,133.09t/data=!3m7!1e1!3m5!1s4DwIvX5APEFpiYIzUHmeyQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-43.08844544062512%26panoid%3D4DwIvX5APEFpiYIzUHmeyQ%26yaw%3D169.43212754826789!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1551" t="n">
+        <v>3192</v>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>221704136</t>
+        </is>
+      </c>
+      <c r="D1551" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 500, 500, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1551" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5964572,-46.9370331,3a,90y,184.87h,142.51t/data=!3m7!1e1!3m5!1sPoqMylBcHJLcyGTHZ9VZeQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-52.50948068290032%26panoid%3DPoqMylBcHJLcyGTHZ9VZeQ%26yaw%3D184.86839519301415!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1552" t="n">
+        <v>3106</v>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>219992894</t>
+        </is>
+      </c>
+      <c r="D1552" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 500, 500, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1552" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5962063,-46.937334,3a,90y,173.85h,123.49t/data=!3m7!1e1!3m5!1s9VMZsB_1YCkE2wxylfZpOw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-33.49073286528434%26panoid%3D9VMZsB_1YCkE2wxylfZpOw%26yaw%3D173.85092184565923!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1553" t="n">
+        <v>3022</v>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>224357682</t>
+        </is>
+      </c>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 399, 399, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1553" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5959731,-46.9376541,3a,75y,147.76h,114.03t/data=!3m7!1e1!3m5!1sQ7NjMcYiqZzTKWu5ADylkg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-24.029904721745908%26panoid%3DQ7NjMcYiqZzTKWu5ADylkg%26yaw%3D147.75545174532357!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1554" t="n">
+        <v>2945</v>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>220854103</t>
+        </is>
+      </c>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>AVENIDA GETULIO VARGAS 381, 381, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1554" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.595779,-46.937883,3a,90y,272.15h,140.86t/data=!3m7!1e1!3m5!1svSEm0DIqpa6ct4mkgabuhQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-50.855343937031506%26panoid%3DvSEm0DIqpa6ct4mkgabuhQ%26yaw%3D272.14887726592144!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1555" t="n">
+        <v>2869</v>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>223455561</t>
+        </is>
+      </c>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>PRACA ARTUR BERNARDES 11, 11, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1555" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5969409,-46.9377501,3a,57.4y,332.37h,107.09t/data=!3m7!1e1!3m5!1sXBOiiRBTq2UVZw6JXN_vpA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-17.08856862324427%26panoid%3DXBOiiRBTq2UVZw6JXN_vpA%26yaw%3D332.36617584947896!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>224357790</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>RUA MARIA RITA DE AGUIAR 18, 18, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1556" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1556" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1556" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '325 R. Francelino Cardoso', cod_id escolhido e de 'RUA MARIA RITA DE AGUIAR 18, 18, CENTRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5972542,-46.9372043,3a,48.9y,80.16h,106.83t/data=!3m7!1e1!3m5!1sX8bdyoULuit8bWTxAdY9PA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-16.827167422082596%26panoid%3DX8bdyoULuit8bWTxAdY9PA%26yaw%3D80.1552016721359!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>220854080</t>
+        </is>
+      </c>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>RUA FRANCELINO CARDOSO 76, 76, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1557" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5971578,-46.9373897,3a,75y,35.23h,131.4t/data=!3m7!1e1!3m5!1s9PjIxpsH5NCiCtHYwA05Tw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-41.400328141715335%26panoid%3D9PjIxpsH5NCiCtHYwA05Tw%26yaw%3D35.22570950563359!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>1891129199</t>
+        </is>
+      </c>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>RUA FRANCELINO CARDOSO 70, 70, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1558" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5970289,-46.9376445,3a,90y,36.42h,122.59t/data=!3m7!1e1!3m5!1sDP13BIPmUSQL4QfkuQskgA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-32.58835488021839%26panoid%3DDP13BIPmUSQL4QfkuQskgA%26yaw%3D36.417788848836!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>2683729726</t>
+        </is>
+      </c>
+      <c r="D1559" t="inlineStr">
+        <is>
+          <t>RUA FRANCELINO CARDOSO 325, 325, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1559" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1559" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1559" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '2 R. Maria Rita de Águiar', cod_id escolhido e de 'RUA FRANCELINO CARDOSO 325, 325, CENTRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5967475,-46.9381032,3a,75y,75.45h,118.56t/data=!3m7!1e1!3m5!1sxEjJe9mRKk4Ck1ef3qgyFg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-28.558251489099803%26panoid%3DxEjJe9mRKk4Ck1ef3qgyFg%26yaw%3D75.45446628804945!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>220854082</t>
+        </is>
+      </c>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>RUA FRANCELINO CARDOSO 0, 0, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1560" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5966054,-46.9383534,3a,90y,18.54h,123.73t/data=!3m7!1e1!3m5!1smDD8CMA58HefzLBl2gYEnQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-33.729701549685345%26panoid%3DmDD8CMA58HefzLBl2gYEnQ%26yaw%3D18.537296686228423!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>219993034</t>
+        </is>
+      </c>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>RUA FRANCELINO CARDOSO 0, 0, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1561" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5970501,-46.9378438,3a,90y,313.74h,125.24t/data=!3m7!1e1!3m5!1saFBhbjlRisWz_k-CviVR4w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-35.23784776633815%26panoid%3DaFBhbjlRisWz_k-CviVR4w%26yaw%3D313.74238238976864!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>2683729725</t>
+        </is>
+      </c>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>RUA MARIA RITA DE AGUIAR 10, 10, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1562" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5970934,-46.9381808,3a,90y,349.96h,114.07t/data=!3m7!1e1!3m5!1s-RwWx_iucLgMO1COH67EEw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-24.067859751921347%26panoid%3D-RwWx_iucLgMO1COH67EEw%26yaw%3D349.96221798759314!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>220854081</t>
+        </is>
+      </c>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>RUA MARIA RITA DE AGUIAR 152, 152, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1563" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5971055,-46.938578,3a,90y,21.17h,112.97t/data=!3m7!1e1!3m5!1sUsz1Rhtge8LcK1IYkewOvA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.970616935349%26panoid%3DUsz1Rhtge8LcK1IYkewOvA%26yaw%3D21.1693190619092!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>224357795</t>
+        </is>
+      </c>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>RUA PRIMEIRO DE MAIO 177, 177, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1564" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1564" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1564" t="inlineStr">
+        <is>
+          <t>confirmar - poste mais proximo (5.3m) tem 76 graus de diferenca de rumo, mas esta perto o suficiente pra ser so ruido de GPS; ATENCAO nome de rua muito diferente: Street View diz o endereco e '334 R. Maria Rita de Águiar', cod_id escolhido e de 'RUA PRIMEIRO DE MAIO 177, 177, CENTRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.59713,-46.9388865,3a,90y,353.05h,123.51t/data=!3m7!1e1!3m5!1sv6w1s3iufMsQCZ_f7RUjJg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-33.50736237778975%26panoid%3Dv6w1s3iufMsQCZ_f7RUjJg%26yaw%3D353.04822879284575!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>220854122</t>
+        </is>
+      </c>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>RUA PRIMEIRO DE MAIO 177, 177, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1565" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1565" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1565" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '334 R. Maria Rita de Águiar', cod_id escolhido e de 'RUA PRIMEIRO DE MAIO 177, 177, CENTRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5971747,-46.939344,3a,48.9y,57.22h,117.38t/data=!3m7!1e1!3m5!1s7y-Ib9PhPlAn4cII4Vy3IA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-27.38396541252021%26panoid%3D7y-Ib9PhPlAn4cII4Vy3IA%26yaw%3D57.22353544637687!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>222494824</t>
+        </is>
+      </c>
+      <c r="D1566" t="inlineStr">
+        <is>
+          <t>RUA MARIA RITA DE AGUIAR 325, 325, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1566" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5971998,-46.9396529,3a,90y,14.86h,124.81t/data=!3m7!1e1!3m5!1spxoyzOlPy96kQrIk26jX8g!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-34.813283684124926%26panoid%3DpxoyzOlPy96kQrIk26jX8g%26yaw%3D14.855214362285505!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>221704222</t>
+        </is>
+      </c>
+      <c r="D1567" t="inlineStr">
+        <is>
+          <t>RUA MARIA RITA DE AGUIAR 274, 274, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1567" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5972277,-46.9399532,3a,75y,298.36h,108.99t/data=!3m7!1e1!3m5!1szgkRcdeiH2QF5KctotL0jw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-18.991754827932795%26panoid%3DzgkRcdeiH2QF5KctotL0jw%26yaw%3D298.3607257370032!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>220854120</t>
+        </is>
+      </c>
+      <c r="D1568" t="inlineStr">
+        <is>
+          <t>RUA MARIA RITA DE AGUIAR 33, 33, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1568" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5972595,-46.9403027,3a,75y,297.29h,112.28t/data=!3m7!1e1!3m5!1s98oBFA94N7oRg7M-mpWGnw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.27961692712408%26panoid%3D98oBFA94N7oRg7M-mpWGnw%26yaw%3D297.28841972816076!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>219992975</t>
+        </is>
+      </c>
+      <c r="D1569" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 387, 387, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1569" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1569" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1569" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '234 R. Maria Rita de Águiar', cod_id escolhido e de 'AVENIDA IMBIARA 387, 387, CENTRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5973502,-46.9390221,3a,90y,255.78h,131.42t/data=!3m7!1e1!3m5!1stQqiODchs_p1N8IVklFVBQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-41.42394052711498%26panoid%3DtQqiODchs_p1N8IVklFVBQ%26yaw%3D255.78363130001216!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>220854121</t>
+        </is>
+      </c>
+      <c r="D1570" t="inlineStr">
+        <is>
+          <t>RUA PRIMEIRO DE MAIO 144, 144, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1570" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5977153,-46.9389859,3a,90y,287.37h,127.89t/data=!3m7!1e1!3m5!1sKDjaHz63cgWKox8o-Pixww!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-37.889373290673504%26panoid%3DKDjaHz63cgWKox8o-Pixww%26yaw%3D287.36801553751815!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>221704166</t>
+        </is>
+      </c>
+      <c r="D1571" t="inlineStr">
+        <is>
+          <t>RUA PRIMEIRO DE MAIO 178, 178, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1571" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5979866,-46.9389612,3a,75y,204.29h,120.73t/data=!3m7!1e1!3m5!1ssqclFjVuF397pvpN9aj6Cw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-30.732979269318818%26panoid%3DsqclFjVuF397pvpN9aj6Cw%26yaw%3D204.29423664805898!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1572" t="n">
+        <v>3104</v>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>220854146</t>
+        </is>
+      </c>
+      <c r="D1572" t="inlineStr">
+        <is>
+          <t>RUA PRIMEIRO DE MAIO 208, 208, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1572" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5983633,-46.9389195,3a,48.9y,201.31h,110.22t/data=!3m7!1e1!3m5!1sT-Apej3gv4YbVEPQTLY3-Q!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-20.217678351554383%26panoid%3DT-Apej3gv4YbVEPQTLY3-Q%26yaw%3D201.3128132967817!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>224357826</t>
+        </is>
+      </c>
+      <c r="D1573" t="inlineStr">
+        <is>
+          <t>RUA PRIMEIRO DE MAIO 234, 234, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1573" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5982541,-46.9395761,3a,90y,359.37h,107.44t/data=!3m7!1e1!3m5!1svafYVu_ARnUAt6tGWbv3og!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-17.43624633428776%26panoid%3DvafYVu_ARnUAt6tGWbv3og%26yaw%3D359.36572891717645!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>223977865</t>
+        </is>
+      </c>
+      <c r="D1574" t="inlineStr">
+        <is>
+          <t>RUA FRANCISCO DOS SANTOS 101, 101, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1574" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5982774,-46.9398806,3a,75y,311.49h,113.28t/data=!3m7!1e1!3m5!1sL6-aEbxt4BSPLCsy9rzt2A!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-23.284796263894563%26panoid%3DL6-aEbxt4BSPLCsy9rzt2A%26yaw%3D311.4915185047878!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>222494862</t>
+        </is>
+      </c>
+      <c r="D1575" t="inlineStr">
+        <is>
+          <t>RUA FRANCISCO DOS SANTOS 71, 71, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1575" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5983257,-46.9402853,3a,75y,354.11h,115.3t/data=!3m7!1e1!3m5!1sDA4lmhFXqzb7OVPMXTgq8A!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-25.3040837831862%26panoid%3DDA4lmhFXqzb7OVPMXTgq8A%26yaw%3D354.10804357911286!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>224357827</t>
+        </is>
+      </c>
+      <c r="D1576" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 501, 501, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1576" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5981327,-46.9381455,3a,63.6y,4.05h,114.68t/data=!3m7!1e1!3m5!1sPG4rgiwiM2AeD4gonPBrnw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-24.683346741964%26panoid%3DPG4rgiwiM2AeD4gonPBrnw%26yaw%3D4.050244503923883!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>223455555</t>
+        </is>
+      </c>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>RUA FRANCISCO DOS SANTOS 245, 245, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1577" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5973317,-46.9407125,3a,58.8y,349.45h,121.13t/data=!3m7!1e1!3m5!1swjWwyy7ETB5JiFdaQOH1VA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-31.133873882189633%26panoid%3DwjWwyy7ETB5JiFdaQOH1VA%26yaw%3D349.4487272531636!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1578" t="n">
+        <v>2683</v>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>220780284</t>
+        </is>
+      </c>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 416, 416, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1578" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5973437,-46.9408893,3a,75y,346.05h,115.69t/data=!3m7!1e1!3m5!1sBcqI7PJn2UV-QTgEoJBneA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-25.69165280359242%26panoid%3DBcqI7PJn2UV-QTgEoJBneA%26yaw%3D346.05178694707905!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>224137692</t>
+        </is>
+      </c>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>RUA HEITOR MONTANDON 46, 46, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1579" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5973558,-46.9411037,3a,75y,329.56h,110.1t/data=!3m7!1e1!3m5!1sR1eEWyTLfVrT7zB4b5xBRQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-20.10189779705695%26panoid%3DR1eEWyTLfVrT7zB4b5xBRQ%26yaw%3D329.5632956126821!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>223976913</t>
+        </is>
+      </c>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>RUA HEITOR MONTANDON 48, 48, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1580" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5973582,-46.9413994,3a,90y,306.02h,129.63t/data=!3m7!1e1!3m5!1sTeeAP4sHppxCBRBqXAbK-A!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-39.630321782039715%26panoid%3DTeeAP4sHppxCBRBqXAbK-A%26yaw%3D306.0249905113782!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>220780274</t>
+        </is>
+      </c>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>RUA HEITOR MONTANDON 77, 77, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1581" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5954404,-46.9405037,3a,75y,68.3h,131.75t/data=!3m7!1e1!3m5!1sMjEnyIU0ZxxdBw4ownV1Rw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-41.750259464494775%26panoid%3DMjEnyIU0ZxxdBw4ownV1Rw%26yaw%3D68.30165404858063!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1582" t="n">
+        <v>2392</v>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>224292788</t>
+        </is>
+      </c>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>RUA FRANCELINO CARDOSO 26, 26, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1582" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5955231,-46.9406482,3a,90y,103.18h,145.76t/data=!3m7!1e1!3m5!1swBB9Dy2-HNuYYW29-JOnDQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-55.764552732609275%26panoid%3DwBB9Dy2-HNuYYW29-JOnDQ%26yaw%3D103.183873914761!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1583" t="n">
+        <v>2398</v>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>224495683</t>
+        </is>
+      </c>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>RUA FRANCELINO CARDOSO 26, 26, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1583" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5954663,-46.9408212,3a,75y,178.82h,120.94t/data=!3m7!1e1!3m5!1sfjnmckdt8GkdV2VoguHYDg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-30.941048024947577%26panoid%3Dfjnmckdt8GkdV2VoguHYDg%26yaw%3D178.82071625415875!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1584" t="n">
+        <v>2337</v>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>223976898</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 188, 188, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1584" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5958491,-46.9407554,3a,90y,255.88h,138.16t/data=!3m7!1e1!3m5!1s3ez4raTH8q3AkgC7VhgB-A!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-48.16120513052323%26panoid%3D3ez4raTH8q3AkgC7VhgB-A%26yaw%3D255.88344599370836!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>224318230</t>
+        </is>
+      </c>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 250, 250, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1585" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5962966,-46.9407178,3a,63.6y,330.63h,114.43t/data=!3m7!1e1!3m5!1sjDOyHhewvLTAvNQIGxg5Rg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-24.433278959289254%26panoid%3DjDOyHhewvLTAvNQIGxg5Rg%26yaw%3D330.62778566786966!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>222494582</t>
+        </is>
+      </c>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 260, 260, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1586" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1586" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1586" t="inlineStr">
+        <is>
+          <t>confirmar - distancia (10.6m, 18 graus) e rumo (46.5m, 17 graus) nao concordam com confianca</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.596586,-46.9406862,3a,75y,311.59h,123.84t/data=!3m7!1e1!3m5!1sMkPCUDGYjKADukWPYIgcqQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-33.84447305425155%26panoid%3DMkPCUDGYjKADukWPYIgcqQ%26yaw%3D311.58619930705476!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>219298253</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 270, 270, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1587" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5968456,-46.940662,3a,75y,214.44h,128.88t/data=!3m7!1e1!3m5!1sjgNJ_2GA2P65x6Kw1ZSeNQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-38.87872560516604%26panoid%3DjgNJ_2GA2P65x6Kw1ZSeNQ%26yaw%3D214.43932126674463!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>219991655</t>
+        </is>
+      </c>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 382, 382, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1588" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5972126,-46.9406219,3a,90y,253.36h,124.32t/data=!3m7!1e1!3m5!1svVVQeKsHKTomYULFj7h0BA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-34.32255203428062%26panoid%3DvVVQeKsHKTomYULFj7h0BA%26yaw%3D253.3624463879976!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1589" t="n">
+        <v>2687</v>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>223976897</t>
+        </is>
+      </c>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 386, 386, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1589" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5974873,-46.9405985,3a,48.9y,207.49h,121.64t/data=!3m7!1e1!3m5!1s4QWWyzTpHNdNFndcD7M4Xg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-31.64332512248778%26panoid%3D4QWWyzTpHNdNFndcD7M4Xg%26yaw%3D207.48679758334757!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>224318231</t>
+        </is>
+      </c>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 444, 444, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1590" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1590" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1590" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '432 BR-452', cod_id escolhido e de 'AVENIDA IMBIARA 444, 444, CENTRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5978472,-46.940567,3a,48.9y,200.74h,121.12t/data=!3m7!1e1!3m5!1sbj0IUPLQg1F9mdRfOe_gkw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-31.116267524035777%26panoid%3Dbj0IUPLQg1F9mdRfOe_gkw%26yaw%3D200.74161848859035!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>219298258</t>
+        </is>
+      </c>
+      <c r="D1591" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 494, 494, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1591" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1591" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1591" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '482 BR-452', cod_id escolhido e de 'AVENIDA IMBIARA 494, 494, CENTRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5982609,-46.9405143,3a,75y,270.37h,124.39t/data=!3m7!1e1!3m5!1sC9OfQIkjEAzyobvhfb6sFg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-34.39150991736908%26panoid%3DC9OfQIkjEAzyobvhfb6sFg%26yaw%3D270.3721187070382!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1592" t="n">
+        <v>2838</v>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>219387109</t>
+        </is>
+      </c>
+      <c r="D1592" t="inlineStr">
+        <is>
+          <t>RUA PADRE ALAOR 132, 132, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1592" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5987031,-46.9404816,3a,75y,327.03h,125.54t/data=!3m7!1e1!3m5!1s9D5co9vvTRPyWtkZ_6gFXA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-35.54163338225018%26panoid%3D9D5co9vvTRPyWtkZ_6gFXA%26yaw%3D327.0267861772797!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>220930709</t>
+        </is>
+      </c>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 0, 0, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1593" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5990022,-46.9404374,3a,75y,257.58h,132.7t/data=!3m7!1e1!3m5!1sMWqZn2yLbtzElmDe4XGvyg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-42.69876742331172%26panoid%3DMWqZn2yLbtzElmDe4XGvyg%26yaw%3D257.58425220735415!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>220316601</t>
+        </is>
+      </c>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 603, 603, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1594" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5993578,-46.9404216,3a,90y,223.78h,131.49t/data=!3m7!1e1!3m5!1s3_Ag0_OBJhNMvljW6Mnm5A!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-41.49022433989816%26panoid%3D3_Ag0_OBJhNMvljW6Mnm5A%26yaw%3D223.7785330980011!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>223390363</t>
+        </is>
+      </c>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 651, 651, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1595" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5997242,-46.9403877,3a,90y,214.69h,132.87t/data=!3m7!1e1!3m5!1sEelXBcFc4YImbepO3m7eig!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-42.86679626398242%26panoid%3DEelXBcFc4YImbepO3m7eig%26yaw%3D214.69121569513172!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>220780206</t>
+        </is>
+      </c>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 665, 665, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1596" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1596" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1596" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '620 MG-428', cod_id escolhido e de 'AVENIDA IMBIARA 665, 665, CENTRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6000416,-46.9403588,3a,90y,249.87h,134.99t/data=!3m7!1e1!3m5!1sOanHs3-t6SRzU-2cmn6Apw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-44.987133821041%26panoid%3DOanHs3-t6SRzU-2cmn6Apw%26yaw%3D249.87270478397892!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>224318209</t>
+        </is>
+      </c>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 754, 754, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1597" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1597" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1597" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '779 MG-428', cod_id escolhido e de 'AVENIDA IMBIARA 754, 754, JOAO RIBEIRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6004972,-46.9403117,3a,90y,216.76h,140.47t/data=!3m7!1e1!3m5!1s1ygvRQX7K6dEnPIYsDWuaA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-50.46808135680416%26panoid%3D1ygvRQX7K6dEnPIYsDWuaA%26yaw%3D216.76205642717042!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>221621723</t>
+        </is>
+      </c>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 890, 890, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1598" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6007763,-46.9402861,3a,90y,225.86h,133.85t/data=!3m7!1e1!3m5!1sNaCLwSwhUlENymWFS0Rryw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-43.845700773096326%26panoid%3DNaCLwSwhUlENymWFS0Rryw%26yaw%3D225.857899493211!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>223390362</t>
+        </is>
+      </c>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 900, 900, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1599" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6010551,-46.9402589,3a,90y,262.65h,129.42t/data=!3m7!1e1!3m5!1s89pb3KbehH2ngGiE7XQLJg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-39.41787747069435%26panoid%3D89pb3KbehH2ngGiE7XQLJg%26yaw%3D262.6533088644674!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>220780204</t>
+        </is>
+      </c>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 940, 940, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1600" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6013352,-46.9402287,3a,90y,268.4h,124.47t/data=!3m7!1e1!3m5!1sV73VnIFY5aHbS_zUw1SjFQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-34.465927353870526%26panoid%3DV73VnIFY5aHbS_zUw1SjFQ%26yaw%3D268.39947413325467!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>221621779</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 960, 960, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1601" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6017136,-46.9402054,3a,90y,209.4h,131.85t/data=!3m7!1e1!3m5!1s3iSYsrhFfINUn2taY1HUEQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-41.85453531185149%26panoid%3D3iSYsrhFfINUn2taY1HUEQ%26yaw%3D209.40387396709974!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>221621722</t>
+        </is>
+      </c>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 990, 990, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1602" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1602" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1602" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '990 BR-452', cod_id escolhido e de 'AVENIDA IMBIARA 990, 990, JOAO RIBEIRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6020906,-46.9401623,3a,90y,242.2h,126.28t/data=!3m7!1e1!3m5!1sZWvomvX3cklUGwhF8xYRjg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-36.275960555895324%26panoid%3DZWvomvX3cklUGwhF8xYRjg%26yaw%3D242.19818483655368!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>223390360</t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 1000, 1000, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1603" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6023774,-46.9401343,3a,75y,219.71h,125.28t/data=!3m7!1e1!3m5!1sKKfNk91fV6wypTbTDia84g!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-35.27896527572763%26panoid%3DKKfNk91fV6wypTbTDia84g%26yaw%3D219.71127305965894!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1604" t="n">
+        <v>3087</v>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>219991636</t>
+        </is>
+      </c>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 1080, 1080, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1604" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6026644,-46.9401292,3a,90y,226.75h,133.93t/data=!3m7!1e1!3m5!1syXx9KLK76h4O5T025H8jXg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-43.928173638364484%26panoid%3DyXx9KLK76h4O5T025H8jXg%26yaw%3D226.74629249555514!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>219298224</t>
+        </is>
+      </c>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 1112, 1112, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1605" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6030418,-46.9401325,3a,90y,224.41h,125.98t/data=!3m7!1e1!3m5!1sKsS9fs5N7JtIfR4-ZqqvzA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-35.98183349481752%26panoid%3DKsS9fs5N7JtIfR4-ZqqvzA%26yaw%3D224.4061734460036!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>219991637</t>
+        </is>
+      </c>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 1130, 1130, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1606" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.603504,-46.9401251,3a,75y,329.89h,114.34t/data=!3m7!1e1!3m5!1sUk56dFiHwme0-2OiE-vruQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-24.344709366823736%26panoid%3DUk56dFiHwme0-2OiE-vruQ%26yaw%3D329.8928325683563!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1607" t="n">
+        <v>3016</v>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>224318226</t>
+        </is>
+      </c>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 1142, 1142, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1607" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.603378,-46.9402284,3a,90y,180.12h,138.25t/data=!3m7!1e1!3m5!1sSvHJAu479Zs5ynMviJwvOA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-48.25032937595125%26panoid%3DSvHJAu479Zs5ynMviJwvOA%26yaw%3D180.11726376890618!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1608" t="n">
+        <v>3028</v>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>221621719</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 1142, 1142, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1608" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6037802,-46.9401254,3a,90y,315.19h,138.09t/data=!3m7!1e1!3m5!1scUmOCK205ceEuTsFMz5k2w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-48.087911328270536%26panoid%3DcUmOCK205ceEuTsFMz5k2w%26yaw%3D315.1938239894892!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>222494577</t>
+        </is>
+      </c>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 1212, 1212, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1609" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1609" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1609" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '1170 MG-428', cod_id escolhido e de 'AVENIDA IMBIARA 1212, 1212, JOAO RIBEIRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6039617,-46.9401272,3a,90y,267.42h,140.53t/data=!3m7!1e1!3m5!1syhNmmEa6uQhX_rjw4p2BTA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-50.52661235290648%26panoid%3DyhNmmEa6uQhX_rjw4p2BTA%26yaw%3D267.42224532145354!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>219991635</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>RUA CELIDONIO AFONSECA E SILVA 56, 56, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1610" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1610" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1610" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '1212 MG-428', cod_id escolhido e de 'RUA CELIDONIO AFONSECA E SILVA 56, 56, JOAO RIBEIRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6042278,-46.9401213,3a,90y,275.44h,138.15t/data=!3m7!1e1!3m5!1sZ8Sqpt-H7fQs-hxSE96mKg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-48.148272754570286%26panoid%3DZ8Sqpt-H7fQs-hxSE96mKg%26yaw%3D275.43739813693423!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1611" t="n">
+        <v>2955</v>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>221621720</t>
+        </is>
+      </c>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 1214, 1214, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1611" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6041532,-46.9401795,3a,65.1y,216.15h,131.55t/data=!3m7!1e1!3m5!1sDSB4Mlspw9TAqf9iX2gSFQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-41.553745522696516%26panoid%3DDSB4Mlspw9TAqf9iX2gSFQ%26yaw%3D216.15417782976553!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1612" t="n">
+        <v>2947</v>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>220780221</t>
+        </is>
+      </c>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 1214, 1214, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1612" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6041931,-46.9404987,3a,90y,188.18h,134.3t/data=!3m7!1e1!3m5!1sjtwq2H8DdMiqryBWUxqqLg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-44.298487027724775%26panoid%3Djtwq2H8DdMiqryBWUxqqLg%26yaw%3D188.18233083248197!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>223977801</t>
+        </is>
+      </c>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>RUA CELIDONIO AFONSECA E SILVA 43, 43, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1613" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6044824,-46.9401226,3a,90y,247.19h,131.92t/data=!3m7!1e1!3m5!1skGETY8DxlawDuauOWSU0Sg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-41.9184679069613%26panoid%3DkGETY8DxlawDuauOWSU0Sg%26yaw%3D247.19385731343618!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>2324475315</t>
+        </is>
+      </c>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 1220, 1220, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1614" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6046938,-46.9401289,3a,90y,245.24h,135.57t/data=!3m7!1e1!3m5!1sUn31E6Za1_iBGhZnpxImYw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-45.57290876666525%26panoid%3DUn31E6Za1_iBGhZnpxImYw%26yaw%3D245.24016677068337!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>224318228</t>
+        </is>
+      </c>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 0, 0, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1615" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6051873,-46.9401068,3a,48.9y,332.18h,116.64t/data=!3m7!1e1!3m5!1smkVPY5959vTTUfQYQ8xZGw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-26.636086710705214%26panoid%3DmkVPY5959vTTUfQYQ8xZGw%26yaw%3D332.1803295151014!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1616" t="n">
+        <v>2875</v>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>223455598</t>
+        </is>
+      </c>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 1395, 1395, SILVERIA</t>
+        </is>
+      </c>
+      <c r="E1616" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.60538,-46.940116,3a,90y,257.21h,136.23t/data=!3m7!1e1!3m5!1sPQYs4xaAXfUehEjXPrCFwg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-46.22807801633718%26panoid%3DPQYs4xaAXfUehEjXPrCFwg%26yaw%3D257.21477128253895!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>219298241</t>
+        </is>
+      </c>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 1423, 1423, SILVERIA</t>
+        </is>
+      </c>
+      <c r="E1617" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1617" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1617" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '1400 BR-146', cod_id escolhido e de 'AVENIDA IMBIARA 1423, 1423, SILVERIA' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6055197,-46.9403977,3a,63.6y,222.39h,137.22t/data=!3m7!1e1!3m5!1sc6dV68Es1g1EwyedBMnkVg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-47.22375427545694%26panoid%3Dc6dV68Es1g1EwyedBMnkVg%26yaw%3D222.39203388669338!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1618" t="n">
+        <v>2760</v>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>223977800</t>
+        </is>
+      </c>
+      <c r="D1618" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 985, 985, FERTIZA</t>
+        </is>
+      </c>
+      <c r="E1618" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6055403,-46.940626,3a,90y,188.31h,122.65t/data=!3m7!1e1!3m5!1shtrn5ZzN21704CbueYFnqQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-32.64918629203811%26panoid%3Dhtrn5ZzN21704CbueYFnqQ%26yaw%3D188.31076520277628!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>219991638</t>
+        </is>
+      </c>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>RUA MARIA MULLER 10, 10, FERTIZA</t>
+        </is>
+      </c>
+      <c r="E1619" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6055719,-46.9409117,3a,90y,167.98h,131.55t/data=!3m7!1e1!3m5!1sQSax-NM6HxGhUDFtrp6YAQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-41.54515754128508%26panoid%3DQSax-NM6HxGhUDFtrp6YAQ%26yaw%3D167.9770507337093!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>223455597</t>
+        </is>
+      </c>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>RUA MARIA MULLER 10, 10, FERTIZA</t>
+        </is>
+      </c>
+      <c r="E1620" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6059288,-46.940898,3a,90y,207.39h,131.83t/data=!3m7!1e1!3m5!1sfqeK9NaT6aHeGE4wQO8pJA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-41.82564276825224%26panoid%3DfqeK9NaT6aHeGE4wQO8pJA%26yaw%3D207.39246724099687!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>224318227</t>
+        </is>
+      </c>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>RUA ARTUR CORREA 60, 60, FERTIZA</t>
+        </is>
+      </c>
+      <c r="E1621" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6002923,-46.9393233,3a,87.4y,306.81h,123.91t/data=!3m7!1e1!3m5!1sUitkRIzCEi_WMV6Lr7Jv4A!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-33.90528975629648%26panoid%3DUitkRIzCEi_WMV6Lr7Jv4A%26yaw%3D306.8134208260122!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1622" t="n">
+        <v>3240</v>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>224318214</t>
+        </is>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>RUA URBANO VILELA 107, 107, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1622" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6003015,-46.9394216,3a,39.4y,12.07h,116.55t/data=!3m7!1e1!3m5!1sY0Q1sMwb-aNRk4OUGrLjHQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-26.55316316537464%26panoid%3DY0Q1sMwb-aNRk4OUGrLjHQ%26yaw%3D12.074566268672662!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1623" t="n">
+        <v>3234</v>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>224413352</t>
+        </is>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>RUA URBANO VILELA 107, 107, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1623" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6002628,-46.9389132,3a,90y,326.02h,135.35t/data=!3m7!1e1!3m5!1sivIpMCZm8SeQyL9IQEMrQw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-45.3539204248826%26panoid%3DivIpMCZm8SeQyL9IQEMrQw%26yaw%3D326.0242161742268!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>223977811</t>
+        </is>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>RUA URBANO VILELA 0, 0, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1624" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6003177,-46.9396134,3a,75y,294.49h,115.92t/data=!3m7!1e1!3m5!1s8ZPLP0MBi2wBf96gyKG7aA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-25.918330390989894%26panoid%3D8ZPLP0MBi2wBf96gyKG7aA%26yaw%3D294.48660561770976!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>223977809</t>
+        </is>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>RUA URBANO VILELA 62, 62, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1625" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1625" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1625" t="inlineStr">
+        <is>
+          <t>confirmar - distancia (12.8m, 20 graus) e rumo (58.1m, 17 graus) nao concordam com confianca</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6003553,-46.9401048,3a,90y,5.26h,121.98t/data=!3m7!1e1!3m5!1siDKdHLgjSTv1gFbthH8DOA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-31.97843232217832%26panoid%3DiDKdHLgjSTv1gFbthH8DOA%26yaw%3D5.261850186903644!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1626" t="n">
+        <v>3103</v>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>220780208</t>
+        </is>
+      </c>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 731, 731, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1626" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6002338,-46.9402261,3a,75y,66.33h,132.07t/data=!3m7!1e1!3m5!1srSum4agbfoW9seKhFF7sxw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-42.06604848595407%26panoid%3DrSum4agbfoW9seKhFF7sxw%26yaw%3D66.33481127723182!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1627" t="n">
+        <v>3085</v>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>223977812</t>
+        </is>
+      </c>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>AVENIDA IMBIARA 731, 731, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1627" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6003019,-46.9414453,3a,75y,232.6h,111.5t/data=!3m7!1e1!3m5!1sbKhE9kAlzWBo35wbvcL23Q!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-21.500315103006486%26panoid%3DbKhE9kAlzWBo35wbvcL23Q%26yaw%3D232.60323857188345!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1628" t="n">
+        <v>2799</v>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>224220203</t>
+        </is>
+      </c>
+      <c r="D1628" t="inlineStr">
+        <is>
+          <t>RUA PAUL HARRIS 166, 166, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1628" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6003395,-46.9415637,3a,90y,257.17h,126.06t/data=!3m7!1e1!3m5!1sUp8SYMTDCWq476lpU0RF4w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-36.0602133296245%26panoid%3DUp8SYMTDCWq476lpU0RF4w%26yaw%3D257.1718856818074!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1629" t="n">
+        <v>2771</v>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>222494618</t>
+        </is>
+      </c>
+      <c r="D1629" t="inlineStr">
+        <is>
+          <t>RUA PAUL HARRIS 166, 166, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1629" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6007244,-46.9415228,3a,90y,51.51h,122.43t/data=!3m7!1e1!3m5!1smy04BL8GpMSlutBBwPIPbQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-32.43005273570127%26panoid%3Dmy04BL8GpMSlutBBwPIPbQ%26yaw%3D51.50751890793638!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>219090471</t>
+        </is>
+      </c>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>RUA BENEDITO SIMOES BORGES 30, 30, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1630" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1630" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1630" t="inlineStr">
+        <is>
+          <t>confirmar - distancia (4.1m, 51 graus) e rumo (42.3m, 50 graus) nao concordam com confianca</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6010143,-46.9414955,3a,90y,117.29h,128.74t/data=!3m7!1e1!3m5!1sXvHUV3L5N-IMkq13mUdyfw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-38.740419387491585%26panoid%3DXvHUV3L5N-IMkq13mUdyfw%26yaw%3D117.29271204428355!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>221094496</t>
+        </is>
+      </c>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>RUA BENEDITO SIMOES BORGES 60, 60, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1631" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6013958,-46.9414574,3a,90y,115.43h,112.92t/data=!3m7!1e1!3m5!1s84qroBi2VYqvU4JKZ1rzng!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.915309653647356%26panoid%3D84qroBi2VYqvU4JKZ1rzng%26yaw%3D115.43423627644611!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>220780278</t>
+        </is>
+      </c>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>RUA JOAO BATISTA FERNANDES 110, 110, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1632" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1632" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1632" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '60 R. Benedito Simões Borges', cod_id escolhido e de 'RUA JOAO BATISTA FERNANDES 110, 110, JOAO RIBEIRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6014512,-46.9412085,3a,90y,358.27h,134.27t/data=!3m7!1e1!3m5!1sulznL7OFwcq1XqAPr3DupQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-44.27066324132568%26panoid%3DulznL7OFwcq1XqAPr3DupQ%26yaw%3D358.2671538868202!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>223390371</t>
+        </is>
+      </c>
+      <c r="D1633" t="inlineStr">
+        <is>
+          <t>RUA JOAO BATISTA FERNANDES 100, 100, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1633" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6014152,-46.9407331,3a,90y,334.4h,132.28t/data=!3m7!1e1!3m5!1sMOZU-ZlZvfNYQQsc2W7S1w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-42.279489865462864%26panoid%3DMOZU-ZlZvfNYQQsc2W7S1w%26yaw%3D334.4024738332467!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>219991697</t>
+        </is>
+      </c>
+      <c r="D1634" t="inlineStr">
+        <is>
+          <t>RUA JOAO BATISTA FERNANDES 55, 55, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1634" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6013131,-46.9420142,3a,75y,13.5h,107.82t/data=!3m7!1e1!3m5!1s5n3dIlUm-H3IrxUuYbeBdg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-17.824871115978283%26panoid%3D5n3dIlUm-H3IrxUuYbeBdg%26yaw%3D13.495325438310925!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>222494617</t>
+        </is>
+      </c>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>RUA JOAO RIBEIRO 104, 104, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1635" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6010184,-46.9420432,3a,90y,68.1h,135.49t/data=!3m7!1e1!3m5!1sFjk7xjg8oC3NE1vF1ywnEw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-45.493613478948646%26panoid%3DFjk7xjg8oC3NE1vF1ywnEw%26yaw%3D68.10278578146611!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>221621764</t>
+        </is>
+      </c>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>RUA JOAO RIBEIRO 84, 84, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1636" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1636" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1636" t="inlineStr">
+        <is>
+          <t>confirmar - poste mais proximo (1.0m) tem 161 graus de diferenca de rumo, mas esta perto o suficiente pra ser so ruido de GPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6008355,-46.9420597,3a,48.9y,14.86h,115.86t/data=!3m7!1e1!3m5!1sXHbtsLQLcepx0r0KcmRxHg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-25.862249776679306%26panoid%3DXHbtsLQLcepx0r0KcmRxHg%26yaw%3D14.863135505432558!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>220853343</t>
+        </is>
+      </c>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>RUA JOAO RIBEIRO 25, 25, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1637" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6003507,-46.9421086,3a,75y,121.12h,120.57t/data=!3m7!1e1!3m5!1sUHPcCirwSyOstR381pJAVw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-30.56815856888572%26panoid%3DUHPcCirwSyOstR381pJAVw%26yaw%3D121.11636216480419!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>223976935</t>
+        </is>
+      </c>
+      <c r="D1638" t="inlineStr">
+        <is>
+          <t>RUA PAUL HARRIS 197, 197, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1638" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1638" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1638" t="inlineStr">
+        <is>
+          <t>confirmar - distancia (5.5m, 60 graus) e rumo (48.9m, 31 graus) nao concordam com confianca</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.600374,-46.9423948,3a,75y,244.02h,122.71t/data=!3m7!1e1!3m5!1suVWTaUEaesP0YqqG0OtoqQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-32.705043993290246%26panoid%3DuVWTaUEaesP0YqqG0OtoqQ%26yaw%3D244.02161734828059!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>219991678</t>
+        </is>
+      </c>
+      <c r="D1639" t="inlineStr">
+        <is>
+          <t>RUA PAUL HARRIS 233, 233, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1639" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.600404,-46.942804,3a,75y,221.19h,129.97t/data=!3m7!1e1!3m5!1s_tovy7r4olB8deZtPkh2ug!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-39.97090802161105%26panoid%3D_tovy7r4olB8deZtPkh2ug%26yaw%3D221.18860986518752!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1640" t="n">
+        <v>2471</v>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>222494611</t>
+        </is>
+      </c>
+      <c r="D1640" t="inlineStr">
+        <is>
+          <t>RUA PAUL HARRIS 295, 295, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1640" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6014152,-46.9407331,3a,90y,333.52h,132.46t/data=!3m7!1e1!3m5!1sMOZU-ZlZvfNYQQsc2W7S1w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-42.45931187128633%26panoid%3DMOZU-ZlZvfNYQQsc2W7S1w%26yaw%3D333.5209523458089!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>219991697</t>
+        </is>
+      </c>
+      <c r="D1641" t="inlineStr">
+        <is>
+          <t>RUA JOAO BATISTA FERNANDES 55, 55, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1641" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1641" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1641" t="inlineStr">
+        <is>
+          <t>COLISAO DE COD_ID - movido pra pasta DUPLICADOS, ver duplicados_para_validar.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6014512,-46.9412085,3a,90y,2.49h,139.08t/data=!3m7!1e1!3m5!1sulznL7OFwcq1XqAPr3DupQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-49.07767963929405%26panoid%3DulznL7OFwcq1XqAPr3DupQ%26yaw%3D2.4899684284229693!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>223390371</t>
+        </is>
+      </c>
+      <c r="D1642" t="inlineStr">
+        <is>
+          <t>RUA JOAO BATISTA FERNANDES 100, 100, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1642" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1642" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1642" t="inlineStr">
+        <is>
+          <t>COLISAO DE COD_ID - movido pra pasta DUPLICADOS, ver duplicados_para_validar.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6017874,-46.9411351,3a,90y,296.89h,129.01t/data=!3m7!1e1!3m5!1sO_Dwz5nITNovT56OUABjEA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-39.012410124083175%26panoid%3DO_Dwz5nITNovT56OUABjEA%26yaw%3D296.8923751623787!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>223976926</t>
+        </is>
+      </c>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>RUA ACHILES NOLLI 46, 46, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1643" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6020604,-46.941106,3a,90y,214.6h,131.63t/data=!3m7!1e1!3m5!1sFXE3XvlhIs1Gw41do2ZPBA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-41.62961189030733%26panoid%3DFXE3XvlhIs1Gw41do2ZPBA%26yaw%3D214.60131405544652!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>223976927</t>
+        </is>
+      </c>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>RUA ACHILES NOLLI 80, 80, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1644" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1644" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1644" t="inlineStr">
+        <is>
+          <t>confirmar - distancia (6.9m, 35 graus) e rumo (45.7m, 31 graus) nao concordam com confianca</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6025048,-46.9410711,3a,90y,304.56h,113.26t/data=!3m7!1e1!3m5!1sB-gIE-pPZxKrKHKxN-iQnQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-23.258237129970297%26panoid%3DB-gIE-pPZxKrKHKxN-iQnQ%26yaw%3D304.5616476651592!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>224318261</t>
+        </is>
+      </c>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>RUA ACHILES NOLLI 125, 125, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1645" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6024131,-46.9408195,3a,90y,140.06h,127.38t/data=!3m7!1e1!3m5!1sHpQkeel_-aRsS3HBAkn5LA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-37.381276050104745%26panoid%3DHpQkeel_-aRsS3HBAkn5LA%26yaw%3D140.06220466606095!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>219298289</t>
+        </is>
+      </c>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>RUA CLAUDIO JOSE DE FARIA 0, 0, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1646" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1646" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1646" t="inlineStr">
+        <is>
+          <t>confirmar - distancia (4.7m, 78 graus) e rumo (63.0m, 49 graus) nao concordam com confianca</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.602379,-46.9405194,3a,90y,164.7h,130.33t/data=!3m7!1e1!3m5!1srIyJLK_69V1NbE9TYekLzQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-40.334804747200735%26panoid%3DrIyJLK_69V1NbE9TYekLzQ%26yaw%3D164.70203440964724!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>220780255</t>
+        </is>
+      </c>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>RUA CLAUDIO JOSE DE FARIA 45, 45, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1647" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6027173,-46.9410477,3a,75y,199.09h,117.99t/data=!3m7!1e1!3m5!1srPIQ1zTZ69VuEWJ9gVEl9Q!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-27.994373739497277%26panoid%3DrPIQ1zTZ69VuEWJ9gVEl9Q%26yaw%3D199.0939257229207!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>223254759</t>
+        </is>
+      </c>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>RUA ACHILES NOLLI 170, 170, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1648" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6030939,-46.9410191,3a,90y,218.33h,128.88t/data=!3m7!1e1!3m5!1sFKkNtd11PgWt6etsJOHUfg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-38.87807171051591%26panoid%3DFKkNtd11PgWt6etsJOHUfg%26yaw%3D218.32854926171268!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>224292792</t>
+        </is>
+      </c>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>RUA ACHILES NOLLI 154, 154, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1649" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6034622,-46.9409972,3a,90y,252.42h,141.35t/data=!3m7!1e1!3m5!1s_CEyjT-cyaZWi7tKxx6mIw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-51.345627462858204%26panoid%3D_CEyjT-cyaZWi7tKxx6mIw%26yaw%3D252.42313123536246!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>219386943</t>
+        </is>
+      </c>
+      <c r="D1650" t="inlineStr">
+        <is>
+          <t>RUA WANTUIR BATISTA DA COSTA 115, 115, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1650" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1650" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1650" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '300 R. Achiles Noli', cod_id escolhido e de 'RUA WANTUIR BATISTA DA COSTA 115, 115, JOAO RIBEIRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6034233,-46.9407885,3a,90y,115.39h,130.18t/data=!3m7!1e1!3m5!1swOq5gfHwwWwmkxoo4ZfSgg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-40.18134216231579%26panoid%3DwOq5gfHwwWwmkxoo4ZfSgg%26yaw%3D115.3921026853691!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>220857495</t>
+        </is>
+      </c>
+      <c r="D1651" t="inlineStr">
+        <is>
+          <t>RUA WANTUIR BATISTA DA COSTA 83, 83, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1651" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6033971,-46.9404884,3a,90y,130h,137.01t/data=!3m7!1e1!3m5!1sqMaIVoeRTr0CfYn58Wr2Zg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-47.00614435412109%26panoid%3DqMaIVoeRTr0CfYn58Wr2Zg%26yaw%3D129.9986819146606!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>221807500</t>
+        </is>
+      </c>
+      <c r="D1652" t="inlineStr">
+        <is>
+          <t>RUA WANTUIR BATISTA DA COSTA 0, 0, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1652" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6034634,-46.9412954,3a,90y,120.3h,125.38t/data=!3m7!1e1!3m5!1so2StpNzntYwakPPhYGlb6g!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-35.37877374022625%26panoid%3Do2StpNzntYwakPPhYGlb6g%26yaw%3D120.30081765687842!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1653" t="n">
+        <v>2805</v>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>220857494</t>
+        </is>
+      </c>
+      <c r="D1653" t="inlineStr">
+        <is>
+          <t>RUA WANTUIR BATISTA DA COSTA 110, 110, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1653" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6035439,-46.9413288,3a,75y,40.73h,134.51t/data=!3m7!1e1!3m5!1s4kJMj1HVXHUy1uJPf-U--w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-44.5122044436161%26panoid%3D4kJMj1HVXHUy1uJPf-U--w%26yaw%3D40.730975607268!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1654" t="n">
+        <v>2795</v>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>223254756</t>
+        </is>
+      </c>
+      <c r="D1654" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1165, 1165, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1654" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6037369,-46.9412194,3a,75y,117.77h,129.77t/data=!3m7!1e1!3m5!1sJ1hbYgHJiAxnOVgYC_EtXg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-39.77128215596153%26panoid%3DJ1hbYgHJiAxnOVgYC_EtXg%26yaw%3D117.76697041835132!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>219916312</t>
+        </is>
+      </c>
+      <c r="D1655" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1100, 1100, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1655" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6040551,-46.9410392,3a,75y,359.66h,125t/data=!3m7!1e1!3m5!1sFWv2uHdUog6XOecvfbpECw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-35.00165488577109%26panoid%3DFWv2uHdUog6XOecvfbpECw%26yaw%3D359.6582789522473!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>224221153</t>
+        </is>
+      </c>
+      <c r="D1656" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1095, 1095, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1656" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6015523,-46.942472,3a,90y,350.33h,122.45t/data=!3m7!1e1!3m5!1sJjXV_-sMhNxxmOMCIVt7UA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-32.449227367742054%26panoid%3DJjXV_-sMhNxxmOMCIVt7UA%26yaw%3D350.3299083492549!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1657" t="n">
+        <v>2598</v>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>219298262</t>
+        </is>
+      </c>
+      <c r="D1657" t="inlineStr">
+        <is>
+          <t>RUA JOAO BATISTA FERNANDES 1170, 1170, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1657" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6015533,-46.9425897,3a,41.2y,51.84h,115.68t/data=!3m7!1e1!3m5!1sgLL5cOuF_vZEM2mA-C2Yzw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-25.675276751554946%26panoid%3DgLL5cOuF_vZEM2mA-C2Yzw%26yaw%3D51.83867756696637!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1658" t="n">
+        <v>2580</v>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>224318295</t>
+        </is>
+      </c>
+      <c r="D1658" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1170, 1170, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1658" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6017972,-46.9424349,3a,75y,68.15h,119.61t/data=!3m7!1e1!3m5!1s7FZC7UEfbvOOEO_qOhOsVw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-29.610360134653945%26panoid%3D7FZC7UEfbvOOEO_qOhOsVw%26yaw%3D68.14529507558984!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>220853344</t>
+        </is>
+      </c>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1160, 1160, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1659" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6020364,-46.9422532,3a,90y,49.57h,122.09t/data=!3m8!1e1!3m6!1sJXYBV1N_vsHkx95WadCIuQ!2e0!5s20110801T000000!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-32.085286408325175%26panoid%3DJXYBV1N_vsHkx95WadCIuQ%26yaw%3D49.567320469300846!7i13312!8i6656?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>222494616</t>
+        </is>
+      </c>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1110, 1110, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1660" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6023358,-46.9420981,3a,66.8y,33.46h,127.89t/data=!3m7!1e1!3m5!1strPZYt-lXoQ_WPmGpOqTUA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-37.88771603236425%26panoid%3DtrPZYt-lXoQ_WPmGpOqTUA%26yaw%3D33.46096636880882!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>221621776</t>
+        </is>
+      </c>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>RUA JOAO RIBEIRO 204, 204, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1661" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1661" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1661" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '1263 Av. Pref. Aracely de Paula', cod_id escolhido e de 'RUA JOAO RIBEIRO 204, 204, JOAO RIBEIRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6024911,-46.941882,3a,90y,178.56h,124.32t/data=!3m7!1e1!3m5!1s0F-yQN-35gHwL7zwM54a7A!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-34.323970797426654%26panoid%3D0F-yQN-35gHwL7zwM54a7A%26yaw%3D178.56099606463164!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1662" t="n">
+        <v>2720</v>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>223390374</t>
+        </is>
+      </c>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>RUA CLAUDIO JOSE DE FARIA 196, 196, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1662" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6026208,-46.9419154,3a,75y,36.66h,114.28t/data=!3m7!1e1!3m5!1sLc-8b0nMZ5-qB6XBrwpoZQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-24.27919208652156%26panoid%3DLc-8b0nMZ5-qB6XBrwpoZQ%26yaw%3D36.66195878029345!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1663" t="n">
+        <v>2723</v>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>222733576</t>
+        </is>
+      </c>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1070, 1070, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1663" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6027981,-46.9418143,3a,75y,67.42h,118.66t/data=!3m7!1e1!3m5!1sgdI4quBm9mo_uVK-WfcFzw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-28.663572819858942%26panoid%3DgdI4quBm9mo_uVK-WfcFzw%26yaw%3D67.42066633466865!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>219386941</t>
+        </is>
+      </c>
+      <c r="D1664" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1060, 1060, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1664" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.602918,-46.9418601,3a,63.6y,278.38h,120.62t/data=!3m7!1e1!3m5!1sijvydegA4c-vCYJEtlz3Cg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-30.61845224478259%26panoid%3DijvydegA4c-vCYJEtlz3Cg%26yaw%3D278.38089824515293!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1665" t="n">
+        <v>2691</v>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>224318292</t>
+        </is>
+      </c>
+      <c r="D1665" t="inlineStr">
+        <is>
+          <t>RUA JOAO RIBEIRO 344, 344, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1665" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6025052,-46.9420962,3a,75y,218.36h,118.28t/data=!3m7!1e1!3m5!1s8-b-Xp0igWLowpYXQ-71xQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-28.281380321720306%26panoid%3D8-b-Xp0igWLowpYXQ-71xQ%26yaw%3D218.35796646516923!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1666" t="n">
+        <v>2648</v>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>221621833</t>
+        </is>
+      </c>
+      <c r="D1666" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1225, 1225, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1666" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6030733,-46.9417679,3a,37.6y,168.58h,108.13t/data=!3m7!1e1!3m5!1skOfCFZZX4Za40Me8AFwalw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-18.130247204501202%26panoid%3DkOfCFZZX4Za40Me8AFwalw%26yaw%3D168.5837526312455!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1667" t="n">
+        <v>2712</v>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>223390339</t>
+        </is>
+      </c>
+      <c r="D1667" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1185, 1185, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1667" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6033258,-46.94187,3a,43y,340.75h,108.58t/data=!3m7!1e1!3m5!1s3uLyRCZiOxNT_YT05sJytg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-18.577563415445198%26panoid%3D3uLyRCZiOxNT_YT05sJytg%26yaw%3D340.7515979864932!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1668" t="n">
+        <v>2682</v>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>219991685</t>
+        </is>
+      </c>
+      <c r="D1668" t="inlineStr">
+        <is>
+          <t>RUA JOAO RIBEIRO 378, 378, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1668" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6018009,-46.9429931,3a,33.5y,188.57h,95.13t/data=!3m7!1e1!3m5!1sDhB_MB5-h2Ut2Zky-Z66Nw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-5.132276596765649%26panoid%3DDhB_MB5-h2Ut2Zky-Z66Nw%26yaw%3D188.56766440933848!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>222494684</t>
+        </is>
+      </c>
+      <c r="D1669" t="inlineStr">
+        <is>
+          <t>RUA ZECA DO ALFREDO 0, 0, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1669" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1669" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1669" t="inlineStr">
+        <is>
+          <t>confirmar - distancia (10.8m, 14 graus) e rumo (50.2m, 6 graus) nao concordam com confianca</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6021954,-46.9429754,3a,48.9y,196.25h,104.46t/data=!3m7!1e1!3m5!1s7WDQvoW71Gts0_ZQYek4uA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-14.458997951442655%26panoid%3D7WDQvoW71Gts0_ZQYek4uA%26yaw%3D196.2506540145598!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>219298359</t>
+        </is>
+      </c>
+      <c r="D1670" t="inlineStr">
+        <is>
+          <t>RUA ZECA DO ALFREDO 140, 140, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1670" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6026707,-46.9429702,3a,90y,304.23h,126.73t/data=!3m7!1e1!3m5!1sZBfrim6TXbpYU8E_BE9saQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-36.730935153995105%26panoid%3DZBfrim6TXbpYU8E_BE9saQ%26yaw%3D304.2325051606261!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1671" t="n">
+        <v>2410</v>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>224318361</t>
+        </is>
+      </c>
+      <c r="D1671" t="inlineStr">
+        <is>
+          <t>RUA ZECA DO ALFREDO 180, 180, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1671" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6026023,-46.9431111,3a,65.1y,103.06h,124.13t/data=!3m7!1e1!3m5!1sHPmWC5K0t7nPb11cSOKqzA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-34.13446694594194%26panoid%3DHPmWC5K0t7nPb11cSOKqzA%26yaw%3D103.0550582641602!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1672" t="n">
+        <v>2389</v>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>224318386</t>
+        </is>
+      </c>
+      <c r="D1672" t="inlineStr">
+        <is>
+          <t>RUA CLAUDIO JOSE DE FARIA 331, 331, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1672" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.602633,-46.9434052,3a,90y,135.14h,136.99t/data=!3m7!1e1!3m5!1smy-IvdVzChMW5Ksod62eNA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-46.991716650207024%26panoid%3Dmy-IvdVzChMW5Ksod62eNA%26yaw%3D135.13652618970946!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>223977067</t>
+        </is>
+      </c>
+      <c r="D1673" t="inlineStr">
+        <is>
+          <t>RUA CLAUDIO JOSE DE FARIA 365, 365, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1673" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6026569,-46.9437164,3a,90y,210.63h,128.7t/data=!3m7!1e1!3m5!1sdi40_APuHUhdLW7lE0H_EA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-38.70191906105276%26panoid%3Ddi40_APuHUhdLW7lE0H_EA%26yaw%3D210.6262409328555!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1674" t="n">
+        <v>2202</v>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>223390455</t>
+        </is>
+      </c>
+      <c r="D1674" t="inlineStr">
+        <is>
+          <t>RUA CLAUDIO JOSE DE FARIA 395, 395, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1674" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6026838,-46.9440068,3a,75y,233.2h,109.67t/data=!3m7!1e1!3m5!1sxcxodHTPQG03dRBR92PvNA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-19.669767217855835%26panoid%3DxcxodHTPQG03dRBR92PvNA%26yaw%3D233.19943700863243!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>223977069</t>
+        </is>
+      </c>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>RUA CLAUDIO JOSE DE FARIA 375, 375, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1675" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6027223,-46.9444755,3a,75y,107.18h,119.92t/data=!3m7!1e1!3m5!1sQomIGWhjzfxLIG2lIp8PHQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-29.923989810812145%26panoid%3DQomIGWhjzfxLIG2lIp8PHQ%26yaw%3D107.17672573164535!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>223390454</t>
+        </is>
+      </c>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>RUA CLAUDIO JOSE DE FARIA 417, 417, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1676" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6030672,-46.9429545,3a,48.9y,340.4h,113.45t/data=!3m7!1e1!3m5!1sZ-T6lnI9iyfCy0QyPeFP-w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-23.445580364256358%26panoid%3DZ-T6lnI9iyfCy0QyPeFP-w%26yaw%3D340.39981480432334!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>219298358</t>
+        </is>
+      </c>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>RUA ZECA DO ALFREDO 234, 234, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1677" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6032477,-46.9429514,3a,90y,208.04h,131.73t/data=!3m7!1e1!3m5!1ssrziRociLe_7ZuXR4VSGpg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-41.73239209861188%26panoid%3DsrziRociLe_7ZuXR4VSGpg%26yaw%3D208.0378628598241!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>222494662</t>
+        </is>
+      </c>
+      <c r="D1678" t="inlineStr">
+        <is>
+          <t>RUA ZECA DO ALFREDO 248, 248, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1678" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6036411,-46.9429278,3a,90y,265.4h,129.63t/data=!3m7!1e1!3m5!1scyoeuYKCwtZhHf9tEUQyHQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-39.62716445484958%26panoid%3DcyoeuYKCwtZhHf9tEUQyHQ%26yaw%3D265.4008073248916!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1679" t="n">
+        <v>2355</v>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>221621831</t>
+        </is>
+      </c>
+      <c r="D1679" t="inlineStr">
+        <is>
+          <t>RUA ZECA DO ALFREDO 300, 300, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1679" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6035928,-46.9430296,3a,75y,111.1h,115.44t/data=!3m7!1e1!3m5!1seQXDtvWXMmZ8t1hOCWQL7g!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-25.437352244571358%26panoid%3DeQXDtvWXMmZ8t1hOCWQL7g%26yaw%3D111.09853157329275!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1680" t="n">
+        <v>2348</v>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>223977009</t>
+        </is>
+      </c>
+      <c r="D1680" t="inlineStr">
+        <is>
+          <t>RUA WANTUIR BATISTA DA COSTA 301, 301, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1680" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6036096,-46.9432127,3a,90y,215.42h,117.25t/data=!3m7!1e1!3m5!1sR4J8prRZbzK-AVzo1ziHKQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-27.248192752078793%26panoid%3DR4J8prRZbzK-AVzo1ziHKQ%26yaw%3D215.41555712748408!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>223977032</t>
+        </is>
+      </c>
+      <c r="D1681" t="inlineStr">
+        <is>
+          <t>RUA WANTUIR BATISTA DA COSTA 331, 331, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1681" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6036262,-46.9434077,3a,75y,248.11h,105.54t/data=!3m7!1e1!3m5!1sUMrjLsfQkAHAwuCyugqmDg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-15.542425446713708%26panoid%3DUMrjLsfQkAHAwuCyugqmDg%26yaw%3D248.10597901078674!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>223390436</t>
+        </is>
+      </c>
+      <c r="D1682" t="inlineStr">
+        <is>
+          <t>RUA WANTUIR BATISTA DA COSTA 351, 351, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1682" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6036455,-46.943603,3a,47.5y,250.89h,94.94t/data=!3m7!1e1!3m5!1sKLcQVNigsUNXX6OpA9T01w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-4.9364983487698595%26panoid%3DKLcQVNigsUNXX6OpA9T01w%26yaw%3D250.89328478721973!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1683" t="n">
+        <v>2152</v>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>222494687</t>
+        </is>
+      </c>
+      <c r="D1683" t="inlineStr">
+        <is>
+          <t>RUA WANTUIR BATISTA DA COSTA 371, 371, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1683" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.603566,-46.9426421,3a,90y,107.34h,122.34t/data=!3m7!1e1!3m5!1sg_hCuiEXcvEiiwhaeQ65Lg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-32.33588837363139%26panoid%3Dg_hCuiEXcvEiiwhaeQ65Lg%26yaw%3D107.33698512656628!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>224318360</t>
+        </is>
+      </c>
+      <c r="D1684" t="inlineStr">
+        <is>
+          <t>RUA WANTUIR BATISTA DA COSTA 281, 281, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1684" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6035381,-46.9422571,3a,90y,174.67h,135.32t/data=!3m7!1e1!3m5!1shl5-_hol1F71gsjt4vh4HQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-45.31897572125024%26panoid%3Dhl5-_hol1F71gsjt4vh4HQ%26yaw%3D174.6680184016818!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>220780303</t>
+        </is>
+      </c>
+      <c r="D1685" t="inlineStr">
+        <is>
+          <t>RUA WANTUIR BATISTA DA COSTA 243, 243, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1685" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.603518,-46.9419463,3a,90y,119.49h,123.87t/data=!3m7!1e1!3m5!1sne1IudFDsp_YhhgbGzmczQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-33.86948891264697%26panoid%3Dne1IudFDsp_YhhgbGzmczQ%26yaw%3D119.49430388984513!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1686" t="n">
+        <v>2646</v>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>219298287</t>
+        </is>
+      </c>
+      <c r="D1686" t="inlineStr">
+        <is>
+          <t>RUA WANTUIR BATISTA DA COSTA 213, 213, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1686" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6038391,-46.9429252,3a,75y,206.48h,111.49t/data=!3m7!1e1!3m5!1sdfOZpxIMvVhxwhmOR3Pbww!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-21.49072261141214%26panoid%3DdfOZpxIMvVhxwhmOR3Pbww%26yaw%3D206.47828178603993!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>223390416</t>
+        </is>
+      </c>
+      <c r="D1687" t="inlineStr">
+        <is>
+          <t>RUA ZECA DO ALFREDO 330, 330, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1687" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.604117,-46.9429183,3a,90y,199.66h,117.39t/data=!3m7!1e1!3m5!1sWdl3eZkglo46BiZupGzdCA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-27.39471923369092%26panoid%3DWdl3eZkglo46BiZupGzdCA%26yaw%3D199.66086884371234!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>221621792</t>
+        </is>
+      </c>
+      <c r="D1688" t="inlineStr">
+        <is>
+          <t>RUA ZECA DO ALFREDO 348, 348, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1688" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1688" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1688" t="inlineStr">
+        <is>
+          <t>confirmar - distancia (10.8m, 8 graus) e rumo (36.1m, 3 graus) nao concordam com confianca</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6043913,-46.9429592,3a,90y,219.08h,106.65t/data=!3m7!1e1!3m5!1s2N-ZRKKeJoV3IObtYPWlmA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-16.65228227012375%26panoid%3D2N-ZRKKeJoV3IObtYPWlmA%26yaw%3D219.0761107356805!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1689" t="n">
+        <v>2283</v>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>220853365</t>
+        </is>
+      </c>
+      <c r="D1689" t="inlineStr">
+        <is>
+          <t>RUA ZECA DO ALFREDO 350, 350, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1689" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6043831,-46.9428568,3a,48.9y,217.71h,100.49t/data=!3m7!1e1!3m5!1sLFF8QlyVbZdOCVDyAwqPlQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-10.486956685257226%26panoid%3DLFF8QlyVbZdOCVDyAwqPlQ%26yaw%3D217.7083658383222!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1690" t="n">
+        <v>2297</v>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>222494653</t>
+        </is>
+      </c>
+      <c r="D1690" t="inlineStr">
+        <is>
+          <t>RUA ZECA DO ALFREDO 350, 350, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1690" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6044176,-46.9432604,3a,90y,239h,101.62t/data=!3m7!1e1!3m5!1sYotBHKzAwLEe2VcOCrTbpA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-11.622105578340893%26panoid%3DYotBHKzAwLEe2VcOCrTbpA%26yaw%3D239.00194562124236!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>219991782</t>
+        </is>
+      </c>
+      <c r="D1691" t="inlineStr">
+        <is>
+          <t>RUA CELIDONIO AFONSECA E SILVA 347, 347, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1691" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6044439,-46.9436705,3a,90y,165.41h,118.38t/data=!3m7!1e1!3m5!1sKy78hjT-Y4JTC1fzCK-qKw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-28.378119639804865%26panoid%3DKy78hjT-Y4JTC1fzCK-qKw%26yaw%3D165.408559911483!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1692" t="n">
+        <v>2095</v>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>221621858</t>
+        </is>
+      </c>
+      <c r="D1692" t="inlineStr">
+        <is>
+          <t>RUA CELIDONIO AFONSECA E SILVA 415, 415, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1692" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6044495,-46.9437705,3a,48.9y,140.61h,110.08t/data=!3m7!1e1!3m5!1sZvdgb1V_0maq6-7c_iQnGg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-20.078444981621118%26panoid%3DZvdgb1V_0maq6-7c_iQnGg%26yaw%3D140.6116362560674!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1693" t="n">
+        <v>2075</v>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>224318371</t>
+        </is>
+      </c>
+      <c r="D1693" t="inlineStr">
+        <is>
+          <t>RUA JOAO MAGALHAES 456, 456, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1693" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6047638,-46.9429093,3a,90y,206.38h,116.15t/data=!3m7!1e1!3m5!1sHkPOC2QXgrT1U0qCrjWRNg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-26.152117549799556%26panoid%3DHkPOC2QXgrT1U0qCrjWRNg%26yaw%3D206.3789153991404!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>223390311</t>
+        </is>
+      </c>
+      <c r="D1694" t="inlineStr">
+        <is>
+          <t>RUA ZECA DO ALFREDO 392, 392, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1694" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6043758,-46.9427643,3a,90y,146.18h,129.24t/data=!3m7!1e1!3m5!1shvrLzZm6vygQffuxXvxVwg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-39.239027021970685%26panoid%3DhvrLzZm6vygQffuxXvxVwg%26yaw%3D146.1821929314865!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>219298326</t>
+        </is>
+      </c>
+      <c r="D1695" t="inlineStr">
+        <is>
+          <t>RUA CELIDONIO AFONSECA E SILVA 305, 305, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1695" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6043514,-46.9424898,3a,90y,172.08h,132.44t/data=!3m7!1e1!3m5!1snAp6b0bDa_3d1LFd67-uPQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-42.44450823680617%26panoid%3DnAp6b0bDa_3d1LFd67-uPQ%26yaw%3D172.0810690409014!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>219991726</t>
+        </is>
+      </c>
+      <c r="D1696" t="inlineStr">
+        <is>
+          <t>RUA CELIDONIO AFONSECA E SILVA 285, 285, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1696" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6043223,-46.9421025,3a,75y,236.83h,112.62t/data=!3m7!1e1!3m5!1s1j7Euroq9wtQw9KTO-O6ng!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.62237623940652%26panoid%3D1j7Euroq9wtQw9KTO-O6ng%26yaw%3D236.82932966354963!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>220853366</t>
+        </is>
+      </c>
+      <c r="D1697" t="inlineStr">
+        <is>
+          <t>RUA CELIDONIO AFONSECA E SILVA 255, 255, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1697" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6043033,-46.9419006,3a,75y,119.59h,113.28t/data=!3m7!1e1!3m5!1sneaIrIWfzxndZEGJVwLxvA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-23.28411667413964%26panoid%3DneaIrIWfzxndZEGJVwLxvA%26yaw%3D119.59130646875478!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>222494652</t>
+        </is>
+      </c>
+      <c r="D1698" t="inlineStr">
+        <is>
+          <t>RUA CELIDONIO AFONSECA E SILVA 187, 187, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1698" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6042705,-46.94141,3a,48.9y,241.24h,107.24t/data=!3m7!1e1!3m5!1sFcFUwhVWuMrMjCBD2P3sBg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-17.23857974169441%26panoid%3DFcFUwhVWuMrMjCBD2P3sBg%26yaw%3D241.23837677648433!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>223976970</t>
+        </is>
+      </c>
+      <c r="D1699" t="inlineStr">
+        <is>
+          <t>RUA CELIDONIO AFONSECA E SILVA 149, 149, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1699" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6047127,-46.9417558,3a,90y,279.26h,122.45t/data=!3m7!1e1!3m5!1sisG_8mwyB11oDPrjSkc4vg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-32.45096803434582%26panoid%3DisG_8mwyB11oDPrjSkc4vg%26yaw%3D279.2634302579371!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>223390310</t>
+        </is>
+      </c>
+      <c r="D1700" t="inlineStr">
+        <is>
+          <t>RUA JOAO RIBEIRO 592, 592, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1700" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6050138,-46.9417413,3a,63.6y,197.26h,110.48t/data=!3m7!1e1!3m5!1sgHK7JUerHfCCYEuzyXTxjw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-20.481942692708785%26panoid%3DgHK7JUerHfCCYEuzyXTxjw%26yaw%3D197.25664495821502!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>223976966</t>
+        </is>
+      </c>
+      <c r="D1701" t="inlineStr">
+        <is>
+          <t>RUA DONATO PINHEIRO DOS SANTOS 166, 166, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1701" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1701" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1701" t="inlineStr">
+        <is>
+          <t>ATENCAO nome de rua muito diferente: Street View diz o endereco e '477 R. João Ribeiro', cod_id escolhido e de 'RUA DONATO PINHEIRO DOS SANTOS 166, 166, JOAO RIBEIRO' - conferir manualmente (nao troquei sozinho, pode ser esquina ou so grafia diferente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.605111,-46.9428947,3a,90y,218.62h,117.72t/data=!3m7!1e1!3m5!1sf6gognIQshxWtG9MyLj8wA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-27.715354595715112%26panoid%3Df6gognIQshxWtG9MyLj8wA%26yaw%3D218.61504578348584!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1702" t="n">
+        <v>2232</v>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>223976965</t>
+        </is>
+      </c>
+      <c r="D1702" t="inlineStr">
+        <is>
+          <t>RUA ZECA DO ALFREDO 434, 434, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1702" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6052279,-46.9429428,3a,75y,0.79h,118.73t/data=!3m7!1e1!3m5!1slEabQ1RCnJsugOOof0xjBA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-28.729963255742064%26panoid%3DlEabQ1RCnJsugOOof0xjBA%26yaw%3D0.7900894804134602!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1703" t="n">
+        <v>2212</v>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>223976964</t>
+        </is>
+      </c>
+      <c r="D1703" t="inlineStr">
+        <is>
+          <t>RUA DONATO PINHEIRO DOS SANTOS 316, 316, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1703" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6052505,-46.9433181,3a,90y,19.88h,127.5t/data=!3m7!1e1!3m5!1sTDW7IbQieWv4b4bBI6wrxQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-37.50082363181585%26panoid%3DTDW7IbQieWv4b4bBI6wrxQ%26yaw%3D19.880565560754647!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>220853304</t>
+        </is>
+      </c>
+      <c r="D1704" t="inlineStr">
+        <is>
+          <t>RUA DONATO PINHEIRO DOS SANTOS 356, 356, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1704" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6052599,-46.9436363,3a,90y,322.02h,116.89t/data=!3m7!1e1!3m5!1s632UeLsFTICP2406Zt0AQg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-26.89290275770746%26panoid%3D632UeLsFTICP2406Zt0AQg%26yaw%3D322.0247430864745!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1705" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>220853305</t>
+        </is>
+      </c>
+      <c r="D1705" t="inlineStr">
+        <is>
+          <t>RUA DONATO PINHEIRO DOS SANTOS 378, 378, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1705" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6052634,-46.943732,3a,75y,28.95h,125.07t/data=!3m7!1e1!3m5!1suVZGXlk1WtXTmDEKS-kngw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-35.06734030679729%26panoid%3DuVZGXlk1WtXTmDEKS-kngw%26yaw%3D28.951154243567817!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1706" t="n">
+        <v>2005</v>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>219991783</t>
+        </is>
+      </c>
+      <c r="D1706" t="inlineStr">
+        <is>
+          <t>RUA JOAO MAGALHAES 500, 500, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="E1706" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6055479,-46.9437374,3a,90y,125.83h,139.44t/data=!3m7!1e1!3m5!1sAKgRpF6R_bu8Sar8e3vbGA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-49.439859124393905%26panoid%3DAKgRpF6R_bu8Sar8e3vbGA%26yaw%3D125.83388953813773!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>219298363</t>
+        </is>
+      </c>
+      <c r="D1707" t="inlineStr">
+        <is>
+          <t>RUA JOSE BARBOSA DE CASTRO 16, 16, FERTIZA</t>
+        </is>
+      </c>
+      <c r="E1707" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6060109,-46.9437216,3a,75y,46.9h,124.94t/data=!3m7!1e1!3m5!1sjKCZnXpaYiBaaLYwT3G1pA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-34.938605251876126%26panoid%3DjKCZnXpaYiBaaLYwT3G1pA%26yaw%3D46.90085074721053!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>219991773</t>
+        </is>
+      </c>
+      <c r="D1708" t="inlineStr">
+        <is>
+          <t>RUA JOSE BARBOSA DE CASTRO 65, 65, FERTIZA</t>
+        </is>
+      </c>
+      <c r="E1708" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6063065,-46.943692,3a,90y,116.35h,136.63t/data=!3m7!1e1!3m5!1s7NMuY9v2-rnRxNfblNndeg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-46.62514707671832%26panoid%3D7NMuY9v2-rnRxNfblNndeg%26yaw%3D116.34823733733165!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>222494703</t>
+        </is>
+      </c>
+      <c r="D1709" t="inlineStr">
+        <is>
+          <t>RUA JOSE BARBOSA DE CASTRO 62, 62, FERTIZA</t>
+        </is>
+      </c>
+      <c r="E1709" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1709" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1709" t="inlineStr">
+        <is>
+          <t>confirmar - distancia (3.6m, 39 graus) e rumo (34.8m, 32 graus) nao concordam com confianca</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.606643,-46.9436216,3a,90y,130.04h,132.39t/data=!3m7!1e1!3m5!1szD8LAV1uF5J9y3fTW1zBfw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-42.386806073657425%26panoid%3DzD8LAV1uF5J9y3fTW1zBfw%26yaw%3D130.03791615159557!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1710" t="n">
+        <v>1838</v>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>223390428</t>
+        </is>
+      </c>
+      <c r="D1710" t="inlineStr">
+        <is>
+          <t>RUA JOSE BARBOSA DE CASTRO 92, 92, FERTIZA</t>
+        </is>
+      </c>
+      <c r="E1710" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6070722,-46.9435239,3a,90y,27.32h,119.4t/data=!3m7!1e1!3m5!1sA8qFDA7osl1Ktvv0BUwJ0w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-29.40462170157103%26panoid%3DA8qFDA7osl1Ktvv0BUwJ0w%26yaw%3D27.323597736984!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>223977016</t>
+        </is>
+      </c>
+      <c r="D1711" t="inlineStr">
+        <is>
+          <t>RUA JOSE BARBOSA DE CASTRO 126, 126, FERTIZA</t>
+        </is>
+      </c>
+      <c r="E1711" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6074252,-46.943442,3a,75y,22.83h,116.06t/data=!3m7!1e1!3m5!1sgb2mi-tX9jk-6EXR_AKWYw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-26.055745226802742%26panoid%3Dgb2mi-tX9jk-6EXR_AKWYw%26yaw%3D22.82847751255779!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>219298365</t>
+        </is>
+      </c>
+      <c r="D1712" t="inlineStr">
+        <is>
+          <t>RUA JOSE BARBOSA DE CASTRO 156, 156, FERTIZA</t>
+        </is>
+      </c>
+      <c r="E1712" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1712" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G1712" t="inlineStr">
+        <is>
+          <t>confirmar - distancia (7.9m, 45 graus) e rumo (87.2m, 36 graus) nao concordam com confianca</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6077173,-46.9433634,3a,90y,126.78h,129.62t/data=!3m7!1e1!3m5!1s6qs_F9rDT1WSNJKM-N0eMA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-39.61886269365863%26panoid%3D6qs_F9rDT1WSNJKM-N0eMA%26yaw%3D126.7795585782165!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1713" t="n">
+        <v>1724</v>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>221621843</t>
+        </is>
+      </c>
+      <c r="D1713" t="inlineStr">
+        <is>
+          <t>RUA SEBASTIAO SANTIAGO 207, 207, FERTIZA</t>
+        </is>
+      </c>
+      <c r="E1713" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6076559,-46.9432773,3a,75y,201.34h,113.54t/data=!3m7!1e1!3m5!1sxrzcdReusMc7SuJMEYsdEQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-23.53604562440617%26panoid%3DxrzcdReusMc7SuJMEYsdEQ%26yaw%3D201.34130591154675!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1714" t="n">
+        <v>1739</v>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>222494712</t>
+        </is>
+      </c>
+      <c r="D1714" t="inlineStr">
+        <is>
+          <t>RUA SEBASTIAO SANTIAGO 207, 207, FERTIZA</t>
+        </is>
+      </c>
+      <c r="E1714" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5868394,-46.9426479,3a,90y,228.32h,127.87t/data=!3m7!1e1!3m5!1sVrH8yNncETg3vIkrNdmMJw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-37.869520655764774%26panoid%3DVrH8yNncETg3vIkrNdmMJw%26yaw%3D228.3182887288013!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1715" t="n">
+        <v>287</v>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>223390413</t>
+        </is>
+      </c>
+      <c r="D1715" t="inlineStr">
+        <is>
+          <t>AVENIDA VEREADOR JOAO SENA 461, 461, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1715" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.586199,-46.9434182,3a,75y,195.72h,111.19t/data=!3m7!1e1!3m5!1sindNZA6hblF6NjgW94xxqw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-21.192903880049982%26panoid%3DindNZA6hblF6NjgW94xxqw%26yaw%3D195.71698277119032!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1716" t="n">
+        <v>132</v>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>220857351</t>
+        </is>
+      </c>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>AVENIDA VEREADOR JOAO SENA 567, 567, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1716" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5859855,-46.9438013,3a,75y,135.67h,118.69t/data=!3m7!1e1!3m5!1sUz-D7wN0D04sYso3JVK8Tw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-28.690472821778698%26panoid%3DUz-D7wN0D04sYso3JVK8Tw%26yaw%3D135.66828670945245!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1717" t="n">
+        <v>94</v>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>223255394</t>
+        </is>
+      </c>
+      <c r="D1717" t="inlineStr">
+        <is>
+          <t>AVENIDA VEREADOR JOAO SENA 617, 617, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1717" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5865938,-46.9433627,3a,75y,350.71h,110.86t/data=!3m7!1e1!3m5!1sMtKfl4gYYhNEzfMP0YyszQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-20.860705935257315%26panoid%3DMtKfl4gYYhNEzfMP0YyszQ%26yaw%3D350.71065753710275!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1718" t="n">
+        <v>169</v>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>223977055</t>
+        </is>
+      </c>
+      <c r="D1718" t="inlineStr">
+        <is>
+          <t>RUA JOAQUIM ANTONIO DUTRA 42, 42, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1718" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5887846,-46.9441391,3a,75y,317.66h,107.86t/data=!3m7!1e1!3m5!1sWHrONX1k_vZrt7sOj24X4w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-17.857571572908114%26panoid%3DWHrONX1k_vZrt7sOj24X4w%26yaw%3D317.6646114752503!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1719" t="n">
+        <v>426</v>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>222496785</t>
+        </is>
+      </c>
+      <c r="D1719" t="inlineStr">
+        <is>
+          <t>RUA DO GARIMPO 104, 104, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1719" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5883059,-46.9408761,3a,57.4y,274.95h,101.15t/data=!3m7!1e1!3m5!1sndMgJiLPvldI4S89MWTeQw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-11.147241322068652%26panoid%3DndMgJiLPvldI4S89MWTeQw%26yaw%3D274.94798413600114!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1720" t="n">
+        <v>801</v>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>223390378</t>
+        </is>
+      </c>
+      <c r="D1720" t="inlineStr">
+        <is>
+          <t>RUA CARVALHO LOPES 38, 38, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1720" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5878126,-46.9414348,3a,41.2y,201.72h,105.43t/data=!3m7!1e1!3m5!1scf2jlAtDN8r9UNqg9DU2VA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-15.432156403748067%26panoid%3Dcf2jlAtDN8r9UNqg9DU2VA%26yaw%3D201.72043975715692!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1721" t="n">
+        <v>590</v>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>224017827</t>
+        </is>
+      </c>
+      <c r="D1721" t="inlineStr">
+        <is>
+          <t>AVENIDA VEREADOR JOAO SENA 95, 95, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1721" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5859752,-46.9411725,3a,90y,308.28h,117.06t/data=!3m7!1e1!3m5!1snmAvs8uu_HP1PWYp3iQFuQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-27.05941225314706%26panoid%3DnmAvs8uu_HP1PWYp3iQFuQ%26yaw%3D308.27636983545545!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1722" t="n">
+        <v>241</v>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>220780254</t>
+        </is>
+      </c>
+      <c r="D1722" t="inlineStr">
+        <is>
+          <t>RUA BENTO ANTONIO 149, 149, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1722" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5858546,-46.9411573,3a,90y,215.33h,117.39t/data=!3m7!1e1!3m5!1sVMsb-30iZK3WTYWmnapTQg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-27.390751174003825%26panoid%3DVMsb-30iZK3WTYWmnapTQg%26yaw%3D215.3341107985702!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1723" t="n">
+        <v>225</v>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>221621780</t>
+        </is>
+      </c>
+      <c r="D1723" t="inlineStr">
+        <is>
+          <t>RUA IMBIACA 157, 157, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1723" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5869046,-46.9399212,3a,90y,135.41h,126.75t/data=!3m7!1e1!3m5!1su8RtqWkYDY_jGTXg5lwkQA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-36.74934154380341%26panoid%3Du8RtqWkYDY_jGTXg5lwkQA%26yaw%3D135.40578262850283!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1724" t="n">
+        <v>520</v>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>223455620</t>
+        </is>
+      </c>
+      <c r="D1724" t="inlineStr">
+        <is>
+          <t>RUA BOM JARDIM 140, 140, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1724" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5861196,-46.938613,3a,37.6y,267.78h,105t/data=!3m7!1e1!3m5!1s7ntl1h2hzPLcCbak_hx8sw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-14.996975009386318%26panoid%3D7ntl1h2hzPLcCbak_hx8sw%26yaw%3D267.77758432030396!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1725" t="n">
+        <v>428</v>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>223977786</t>
+        </is>
+      </c>
+      <c r="D1725" t="inlineStr">
+        <is>
+          <t>RUA ABDANUR ELIAS 67, 67, RICA</t>
+        </is>
+      </c>
+      <c r="E1725" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5837856,-46.9371617,3a,48.9y,73.14h,118.42t/data=!3m7!1e1!3m5!1sxQYo8aR30QAGWLdncmA9-Q!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-28.420238848658485%26panoid%3DxQYo8aR30QAGWLdncmA9-Q%26yaw%3D73.14025002041305!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1726" t="n">
+        <v>96</v>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>221807375</t>
+        </is>
+      </c>
+      <c r="D1726" t="inlineStr">
+        <is>
+          <t>AVENIDA DAMASO DRUMMOND 2165, 2165, RICA</t>
+        </is>
+      </c>
+      <c r="E1726" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5933051,-46.9428263,3a,63.6y,120.74h,116.36t/data=!3m7!1e1!3m5!1sIXoIV0TIvHIDBBJhMnxDGw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-26.357344361098285%26panoid%3DIXoIV0TIvHIDBBJhMnxDGw%26yaw%3D120.73964745156132!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1727" t="n">
+        <v>1501</v>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>221621837</t>
+        </is>
+      </c>
+      <c r="D1727" t="inlineStr">
+        <is>
+          <t>RUA TENENTE JOAQUIM DE AVILA 23, 23, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1727" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5913008,-46.9434971,3a,90y,329.73h,126t/data=!3m7!1e1!3m5!1sGqRMkgF2v5OyyGZc8a0sHA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-35.99939265734298%26panoid%3DGqRMkgF2v5OyyGZc8a0sHA%26yaw%3D329.73211743903323!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1728" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>222494694</t>
+        </is>
+      </c>
+      <c r="D1728" t="inlineStr">
+        <is>
+          <t>RUA RIO BRANCO 178, 178, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1728" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5891471,-46.939405,3a,45y,180.27h,106.18t/data=!3m7!1e1!3m5!1s7bJ6Csna35Pnf4R5hcHJIw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-16.17858065380527%26panoid%3D7bJ6Csna35Pnf4R5hcHJIw%26yaw%3D180.2686714649891!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1729" t="n">
+        <v>1075</v>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>222494826</t>
+        </is>
+      </c>
+      <c r="D1729" t="inlineStr">
+        <is>
+          <t>AVENIDA VEREADOR JOAO SENA 143, 143, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1729" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.591389,-46.9468485,3a,90y,273.83h,123.32t/data=!3m7!1e1!3m5!1stIIqSoVOkiiUT8ff12au0A!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-33.315948952119626%26panoid%3DtIIqSoVOkiiUT8ff12au0A%26yaw%3D273.82704161770545!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1730" t="n">
+        <v>470</v>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>221621571</t>
+        </is>
+      </c>
+      <c r="D1730" t="inlineStr">
+        <is>
+          <t>RUA IPIAO 400, 400, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1730" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5925681,-46.9465588,3a,90y,225.51h,115.71t/data=!3m7!1e1!3m5!1s8o3wvL_tur1dGCuWsJsWrQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-25.70510522409498%26panoid%3D8o3wvL_tur1dGCuWsJsWrQ%26yaw%3D225.50956572265218!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1731" t="n">
+        <v>706</v>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>222494431</t>
+        </is>
+      </c>
+      <c r="D1731" t="inlineStr">
+        <is>
+          <t>RUA UBERABA 515, 515, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1731" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5880028,-46.9453903,3a,75y,221.39h,122.47t/data=!3m7!1e1!3m5!1s9o6jYEYhCaqNIMiDtcxh0w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-32.4727349564462%26panoid%3D9o6jYEYhCaqNIMiDtcxh0w%26yaw%3D221.38552978119256!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1732" t="n">
+        <v>184</v>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>223976794</t>
+        </is>
+      </c>
+      <c r="D1732" t="inlineStr">
+        <is>
+          <t>RUA DA CONSOLACAO 341, 341, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1732" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5859328,-46.9451645,3a,90y,99.77h,123.27t/data=!3m7!1e1!3m5!1syidFa0ycbpDHOpWUNcmJZA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-33.26663535123551%26panoid%3DyidFa0ycbpDHOpWUNcmJZA%26yaw%3D99.7725286749026!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1733" t="n">
+        <v>40</v>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>222494492</t>
+        </is>
+      </c>
+      <c r="D1733" t="inlineStr">
+        <is>
+          <t>AVENIDA JOAO PAULO II 105, 105, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1733" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5854658,-46.9448877,3a,90y,153.39h,116.76t/data=!3m7!1e1!3m5!1sM49egrCmHXOk_hYpCqcaBw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-26.757444522637684%26panoid%3DM49egrCmHXOk_hYpCqcaBw%26yaw%3D153.39321730533067!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1734" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>222494491</t>
+        </is>
+      </c>
+      <c r="D1734" t="inlineStr">
+        <is>
+          <t>AVENIDA JOAO PAULO II 35, 35, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1734" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5931747,-46.9468364,3a,90y,50.1h,113.42t/data=!3m8!1e1!3m6!1sqNR1_UsnqkRzy6Y7TBbRkg!2e0!5s20210901T000000!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-23.418916623759543%26panoid%3DqNR1_UsnqkRzy6Y7TBbRkg%26yaw%3D50.103298205067055!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1735" t="n">
+        <v>750</v>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>1496653043</t>
+        </is>
+      </c>
+      <c r="D1735" t="inlineStr">
+        <is>
+          <t>RUA SANTA JULIANA 501, 501, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1735" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5933101,-46.9467062,3a,90y,325.3h,123.91t/data=!3m7!1e1!3m5!1sn5ujMmEi1NRiYB9g3nk3ug!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-33.910465926343505%26panoid%3Dn5ujMmEi1NRiYB9g3nk3ug%26yaw%3D325.30242898754904!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1736" t="n">
+        <v>792</v>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>1496653047</t>
+        </is>
+      </c>
+      <c r="D1736" t="inlineStr">
+        <is>
+          <t>RUA LAURINDO BALEEIRO 46, 46, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1736" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5944984,-46.9470311,3a,90y,293.7h,118.15t/data=!3m7!1e1!3m5!1sMEfBdlMFKDfR9Zha1GArPA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-28.145233665355306%26panoid%3DMEfBdlMFKDfR9Zha1GArPA%26yaw%3D293.6989929380946!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1737" t="n">
+        <v>870</v>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>1496653283</t>
+        </is>
+      </c>
+      <c r="D1737" t="inlineStr">
+        <is>
+          <t>RUA MODESTO CRISTINO FILHO 290, 290, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1737" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5950557,-46.947187,3a,48.9y,350.85h,112.66t/data=!3m7!1e1!3m5!1sNaNzrerqq_caiOBUoArmeQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.65955174639643%26panoid%3DNaNzrerqq_caiOBUoArmeQ%26yaw%3D350.84724193614187!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1738" t="n">
+        <v>903</v>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>222494413</t>
+        </is>
+      </c>
+      <c r="D1738" t="inlineStr">
+        <is>
+          <t>RUA LAURINDO BALEEIRO 25, 25, SANTA LUZIA</t>
+        </is>
+      </c>
+      <c r="E1738" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5952252,-46.9472396,3a,90y,282.6h,134.83t/data=!3m7!1e1!3m5!1sgnAfD4PrqQlLUSThxnWXZQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-44.82971337747247%26panoid%3DgnAfD4PrqQlLUSThxnWXZQ%26yaw%3D282.6027885679023!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1739" t="n">
+        <v>918</v>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>221621581</t>
+        </is>
+      </c>
+      <c r="D1739" t="inlineStr">
+        <is>
+          <t>RUA ALEXANDRE DUMONT 370, 370, SANTA LUZIA</t>
+        </is>
+      </c>
+      <c r="E1739" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5953321,-46.9472756,3a,41.2y,206.09h,105.98t/data=!3m7!1e1!3m5!1sgvaNF8Cil7fpghZTHmXu8w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-15.98476154913881%26panoid%3DgvaNF8Cil7fpghZTHmXu8w%26yaw%3D206.08582537621453!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1740" t="n">
+        <v>933</v>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>220780053</t>
+        </is>
+      </c>
+      <c r="D1740" t="inlineStr">
+        <is>
+          <t>RUA ALEXANDRE DUMONT 475, 475, SANTA LUZIA</t>
+        </is>
+      </c>
+      <c r="E1740" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5952444,-46.9475375,3a,75y,265.87h,106.36t/data=!3m7!1e1!3m5!1sLPUCVZW2wGCFhkYF50kHVw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-16.356697925815382%26panoid%3DLPUCVZW2wGCFhkYF50kHVw%26yaw%3D265.87187161750734!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1741" t="n">
+        <v>846</v>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>223976805</t>
+        </is>
+      </c>
+      <c r="D1741" t="inlineStr">
+        <is>
+          <t>RUA ALEXANDRE DUMONT 525, 525, SANTA LUZIA</t>
+        </is>
+      </c>
+      <c r="E1741" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5963461,-46.9481086,3a,75y,134.17h,124.29t/data=!3m7!1e1!3m5!1s1qYWiGxlseB5kEpa8V_fyA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-34.28821617372839%26panoid%3D1qYWiGxlseB5kEpa8V_fyA%26yaw%3D134.1689991183809!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1742" t="n">
+        <v>848</v>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>224292613</t>
+        </is>
+      </c>
+      <c r="D1742" t="inlineStr">
+        <is>
+          <t>AVENIDA JOAO PAULO II 1205, 1205, SANTA LUZIA</t>
+        </is>
+      </c>
+      <c r="E1742" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5935481,-46.9452271,3a,63.6y,12.66h,114.38t/data=!3m7!1e1!3m5!1siKyG9hGUoHSQ18tqWw09VQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-24.375838288837215%26panoid%3DiKyG9hGUoHSQ18tqWw09VQ%26yaw%3D12.663740805554502!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1743" t="n">
+        <v>1108</v>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>224318084</t>
+        </is>
+      </c>
+      <c r="D1743" t="inlineStr">
+        <is>
+          <t>RUA FUNCIONARIO JOAO ROSA 105, 105, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1743" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5965887,-46.9470055,3a,90y,57.08h,124.08t/data=!3m7!1e1!3m5!1sjF4JvQpNMubHQwUzb8q1ag!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-34.08197777265438%26panoid%3DjF4JvQpNMubHQwUzb8q1ag%26yaw%3D57.077267414165675!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1744" t="n">
+        <v>1113</v>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>219991920</t>
+        </is>
+      </c>
+      <c r="D1744" t="inlineStr">
+        <is>
+          <t>RUA ELOI TEIXEIRA 71, 71, SANTA LUZIA</t>
+        </is>
+      </c>
+      <c r="E1744" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5925279,-46.9377839,3a,90y,341.06h,122.29t/data=!3m7!1e1!3m5!1sLtGCuKxCbtm506Uc4C9bqA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-32.291548942773204%26panoid%3DLtGCuKxCbtm506Uc4C9bqA%26yaw%3D341.0572452334893!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1745" t="n">
+        <v>2069</v>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>219992885</t>
+        </is>
+      </c>
+      <c r="D1745" t="inlineStr">
+        <is>
+          <t>RUA PRESIDENTE OLEGARIO MACIEL 190, 190, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1745" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5931566,-46.9362766,3a,90y,266.06h,118t/data=!3m7!1e1!3m5!1saqAUmqmlbO8rCn3Q3HtcGQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-27.997166318149254%26panoid%3DaqAUmqmlbO8rCn3Q3HtcGQ%26yaw%3D266.0620682067779!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1746" t="n">
+        <v>2376</v>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>219992945</t>
+        </is>
+      </c>
+      <c r="D1746" t="inlineStr">
+        <is>
+          <t>RUA ALMEIDA CAMPOS 100, 100, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1746" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5934511,-46.9388874,3a,53.4y,120.53h,118.07t/data=!3m7!1e1!3m5!1sEHve4xJ0uBsgwEVDfzLxRg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-28.073804075605736%26panoid%3DEHve4xJ0uBsgwEVDfzLxRg%26yaw%3D120.53102163647617!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1747" t="n">
+        <v>2168</v>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>223455661</t>
+        </is>
+      </c>
+      <c r="D1747" t="inlineStr">
+        <is>
+          <t>RUA CAPITAO IZIDRO 197, 197, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1747" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5887464,-46.9348229,3a,90y,147.76h,122.3t/data=!3m7!1e1!3m5!1soq7Z1T3WYCdsdzKC6D0ItQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-32.30330639839357%26panoid%3Doq7Z1T3WYCdsdzKC6D0ItQ%26yaw%3D147.7602049531739!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1748" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>224358092</t>
+        </is>
+      </c>
+      <c r="D1748" t="inlineStr">
+        <is>
+          <t>RUA LIMIRIO AFONSO 396, 396, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1748" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5890354,-46.9348956,3a,90y,149.05h,117.31t/data=!3m7!1e1!3m5!1s6O3y781nKerknVfyZmtrng!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-27.31323929808528%26panoid%3D6O3y781nKerknVfyZmtrng%26yaw%3D149.04902386544967!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1749" t="n">
+        <v>1284</v>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>220854284</t>
+        </is>
+      </c>
+      <c r="D1749" t="inlineStr">
+        <is>
+          <t>RUA LIMIRIO AFONSO 386, 386, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1749" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.589247,-46.934998,3a,75y,174.11h,113.45t/data=!3m7!1e1!3m5!1srzulSuOrvtyLzLfLIiBcHg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-23.448490854589323%26panoid%3DrzulSuOrvtyLzLfLIiBcHg%26yaw%3D174.11014482169708!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1750" t="n">
+        <v>1336</v>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>219992834</t>
+        </is>
+      </c>
+      <c r="D1750" t="inlineStr">
+        <is>
+          <t>RUA LIMIRIO AFONSO 330, 330, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1750" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.589492,-46.9351283,3a,75y,179.68h,114.12t/data=!3m7!1e1!3m5!1s-sPVYfEH-2SDdPaDLJMlNQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-24.11630316858114%26panoid%3D-sPVYfEH-2SDdPaDLJMlNQ%26yaw%3D179.67728887844987!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1751" t="n">
+        <v>1397</v>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>219385237</t>
+        </is>
+      </c>
+      <c r="D1751" t="inlineStr">
+        <is>
+          <t>RUA LIMIRIO AFONSO 300, 300, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1751" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5897586,-46.9352144,3a,75y,162.64h,122.31t/data=!3m7!1e1!3m5!1sESmnQYrWm1izUv8NOim4PA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-32.310740424217855%26panoid%3DESmnQYrWm1izUv8NOim4PA%26yaw%3D162.63546078710763!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1752" t="n">
+        <v>1459</v>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t>224358044</t>
+        </is>
+      </c>
+      <c r="D1752" t="inlineStr">
+        <is>
+          <t>RUA LIMIRIO AFONSO 293, 293, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1752" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5901093,-46.9352683,3a,89.5y,136.76h,114.87t/data=!3m7!1e1!3m5!1syqkyfzHYwaenOURNxM1v0g!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-24.87008580139492%26panoid%3DyqkyfzHYwaenOURNxM1v0g%26yaw%3D136.76462966170686!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1753" t="n">
+        <v>1539</v>
+      </c>
+      <c r="C1753" t="inlineStr">
+        <is>
+          <t>223978140</t>
+        </is>
+      </c>
+      <c r="D1753" t="inlineStr">
+        <is>
+          <t>RUA LIMIRIO AFONSO 227, 227, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1753" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5885443,-46.9339857,3a,90y,77.03h,139.82t/data=!3m7!1e1!3m5!1skULaTeYN16Le4VZosUYBeA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-49.81786478703131%26panoid%3DkULaTeYN16Le4VZosUYBeA%26yaw%3D77.0265948629253!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B1754" t="n">
+        <v>1159</v>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>408801682</t>
+        </is>
+      </c>
+      <c r="D1754" t="inlineStr">
+        <is>
+          <t>RUA ALEXANDRE GONDIM 510, 510, CENTRO</t>
+        </is>
+      </c>
+      <c r="E1754" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1272"/>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" priority="2" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
@@ -38145,6 +46043,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1206" display="https://www.google.com/maps/@-19.5934388,-46.9365385,3a,75y,3.11h,120.54t/data=!3m7!1e1!3m5!1skk4vfjOpTZBa-ZcBXP2uhA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-30.541386432541316%26panoid%3Dkk4vfjOpTZBa-ZcBXP2uhA%26yaw%3D3.105141984690774!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1238" display="https://www.google.com/maps/@-19.5926082,-46.9347985,3a,90y,43.27h,128.58t/data=!3m7!1e1!3m5!1sXl014UelD-1Nj1FpGQjZwg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-38.579963945138445%26panoid%3DXl014UelD-1Nj1FpGQjZwg%26yaw%3D43.2735636166437!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D" r:id="rId227"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1292" display="https://www.google.com/maps/@-19.5870354,-46.9361821,3a,90y,34.42h,138.32t/data=!3m7!1e1!3m5!1sEVF-ySLUQb9Nbr9lD52Y5Q!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-48.32479404868988%26panoid%3DEVF-ySLUQb9Nbr9lD52Y5Q%26yaw%3D34.41794523794839!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1628" display="https://www.google.com/maps/@-19.6003019,-46.9414453,3a,75y,232.6h,111.5t/data=!3m7!1e1!3m5!1sbKhE9kAlzWBo35wbvcL23Q!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-21.500315103006486%26panoid%3DbKhE9kAlzWBo35wbvcL23Q%26yaw%3D232.60323857188345!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1742" display="https://www.google.com/maps/@-19.5963461,-46.9481086,3a,75y,134.17h,124.29t/data=!3m7!1e1!3m5!1s1qYWiGxlseB5kEpa8V_fyA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-34.28821617372839%26panoid%3D1qYWiGxlseB5kEpa8V_fyA%26yaw%3D134.1689991183809!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D" r:id="rId230"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
